--- a/base_datas/mediana_uf_detalhamento.xlsx
+++ b/base_datas/mediana_uf_detalhamento.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
@@ -603,115 +603,118 @@
         </is>
       </c>
       <c r="B2">
-        <v>266.6326966485371</v>
+        <v>283.9583954907779</v>
       </c>
       <c r="C2">
-        <v>41.56797046009988</v>
+        <v>39.80510115453872</v>
       </c>
       <c r="D2">
-        <v>4369.811811135316</v>
+        <v>4759.685129558606</v>
       </c>
       <c r="E2">
-        <v>95.98708203625677</v>
+        <v>145.0513119290826</v>
       </c>
       <c r="F2">
-        <v>252.0553078843906</v>
+        <v>279.239839568117</v>
       </c>
       <c r="G2">
-        <v>6.64702784455546</v>
+        <v>11.10129639374646</v>
       </c>
       <c r="H2">
-        <v>36.7440172635017</v>
+        <v>34.49796639466256</v>
       </c>
       <c r="I2">
-        <v>139.0290148303992</v>
+        <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>39.30365226149057</v>
+        <v>39.80510115453872</v>
       </c>
       <c r="K2">
-        <v>1.267677186271374</v>
+        <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2416.95276108023</v>
+        <v>2739.744731038375</v>
       </c>
       <c r="M2">
-        <v>727.6026020234522</v>
+        <v>770.5855750411912</v>
       </c>
       <c r="N2">
-        <v>1193.021702091091</v>
+        <v>1313.985043231271</v>
       </c>
       <c r="O2">
-        <v>82.30498635173528</v>
+        <v>121.9991253113552</v>
       </c>
       <c r="P2">
-        <v>0.800075275431781</v>
+        <v>5.567369628518485</v>
       </c>
       <c r="S2">
-        <v>3.397293039243703</v>
+        <v>0.3205017313855276</v>
       </c>
       <c r="T2">
-        <v>10.53314039211167</v>
+        <v>8.254262402294792</v>
       </c>
       <c r="U2">
-        <v>7.875878395640706</v>
+        <v>20.20036474962382</v>
       </c>
       <c r="V2">
-        <v>92.99415179052477</v>
+        <v>90.02096352252764</v>
       </c>
       <c r="W2">
-        <v>115.4099893611632</v>
+        <v>130.1075390437837</v>
       </c>
       <c r="Z2">
-        <v>9.356339622548228E-15</v>
+        <v>2.941785340737871E-14</v>
       </c>
       <c r="AA2">
-        <v>3.653760958046337</v>
+        <v>4.732662670168948</v>
       </c>
       <c r="AB2">
-        <v>3.53251853799903</v>
+        <v>8.802885619871919</v>
       </c>
       <c r="AC2">
-        <v>9.956065406555407E-17</v>
+        <v>-1.408619160560911E-16</v>
       </c>
       <c r="AF2">
-        <v>36.7440172635017</v>
+        <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1220.918236249345</v>
+        <v>1420.316144546597</v>
       </c>
       <c r="AJ2">
-        <v>21.93269041382923</v>
+        <v>24.43361282342864</v>
       </c>
       <c r="AK2">
-        <v>646.760110597788</v>
+        <v>697.5568566191579</v>
       </c>
       <c r="AL2">
-        <v>134.2172854542909</v>
+        <v>138.6253725730148</v>
       </c>
       <c r="AM2">
-        <v>148.8074788070989</v>
+        <v>210.4724438042965</v>
       </c>
       <c r="AN2">
-        <v>50.75076195932398</v>
+        <v>32.21932287438311</v>
       </c>
       <c r="AO2">
-        <v>206.149550608988</v>
+        <v>207.7041951684839</v>
       </c>
       <c r="AP2">
-        <v>671.153856449593</v>
+        <v>647.8717564960864</v>
       </c>
       <c r="AQ2">
-        <v>35.9614601191341</v>
+        <v>43.65787379404382</v>
       </c>
       <c r="AR2">
-        <v>2.314565399183433</v>
+        <v>2.489077104813607</v>
       </c>
       <c r="AS2">
-        <v>3.880808937267259</v>
+        <v>6.021043940264216</v>
+      </c>
+      <c r="AT2">
+        <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>14.0494900201429</v>
+        <v>40.44255735079063</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -724,121 +727,124 @@
         </is>
       </c>
       <c r="B3">
-        <v>294.1259045643154</v>
+        <v>341.2111347016007</v>
       </c>
       <c r="C3">
-        <v>247.8005182010886</v>
+        <v>259.3472432054568</v>
       </c>
       <c r="D3">
-        <v>7156.514930238858</v>
+        <v>8018.469716132185</v>
       </c>
       <c r="E3">
-        <v>214.0420135933441</v>
+        <v>231.9742618959338</v>
       </c>
       <c r="F3">
-        <v>274.5102338704621</v>
+        <v>327.6135269189371</v>
       </c>
       <c r="G3">
-        <v>7.38824547963913</v>
+        <v>9.009045629556811</v>
       </c>
       <c r="H3">
-        <v>53.022198298685</v>
+        <v>82.99977930805608</v>
       </c>
       <c r="I3">
-        <v>200.3960416740921</v>
+        <v>198.5066795515491</v>
       </c>
       <c r="J3">
-        <v>90.31133303847855</v>
+        <v>102.6400065879698</v>
       </c>
       <c r="K3">
-        <v>-7.411684078877877E-15</v>
+        <v>1.159420708809301E-14</v>
       </c>
       <c r="L3">
-        <v>4609.625613850996</v>
+        <v>5257.196750971281</v>
       </c>
       <c r="M3">
-        <v>994.4219684651392</v>
+        <v>1041.368728120803</v>
       </c>
       <c r="N3">
-        <v>1462.235461936437</v>
+        <v>1566.593200656242</v>
       </c>
       <c r="O3">
-        <v>131.7399398797595</v>
+        <v>180.8912265697908</v>
       </c>
       <c r="P3">
-        <v>29.26911561968519</v>
+        <v>40.19938480128923</v>
       </c>
       <c r="S3">
-        <v>5.808917334644748</v>
+        <v>11.13753632755408</v>
       </c>
       <c r="T3">
-        <v>5.293483540881375</v>
+        <v>6.021365230217262</v>
       </c>
       <c r="U3">
-        <v>7.788893939078486</v>
+        <v>5.831349378575656</v>
       </c>
       <c r="V3">
-        <v>110.0247852814434</v>
+        <v>100.8135594191041</v>
       </c>
       <c r="W3">
-        <v>122.6934176085433</v>
+        <v>160.0005603313581</v>
       </c>
       <c r="Z3">
-        <v>1.403778148160314E-14</v>
+        <v>2.385078362492537E-14</v>
       </c>
       <c r="AA3">
-        <v>5.910135838749436</v>
+        <v>7.025822281167109</v>
       </c>
       <c r="AB3">
-        <v>2.895904845424574</v>
+        <v>3.020586624262398</v>
       </c>
       <c r="AC3">
-        <v>3.161336327099198E-17</v>
+        <v>-9.367542504613536E-17</v>
+      </c>
+      <c r="AE3">
+        <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>86.97885856756288</v>
+        <v>108.3593809423199</v>
       </c>
       <c r="AG3">
-        <v>1.046027082123138</v>
+        <v>0.1124137542488116</v>
       </c>
       <c r="AH3">
-        <v>2276.579113070539</v>
+        <v>2588.354052280334</v>
       </c>
       <c r="AJ3">
-        <v>47.29368601314449</v>
+        <v>50.31833502661729</v>
       </c>
       <c r="AK3">
-        <v>847.2655979094473</v>
+        <v>914.9533806939953</v>
       </c>
       <c r="AL3">
-        <v>205.117916730212</v>
+        <v>191.3091640218877</v>
       </c>
       <c r="AM3">
-        <v>732.1482649219183</v>
+        <v>1092.255460645058</v>
       </c>
       <c r="AN3">
-        <v>38.79938684740019</v>
+        <v>35.00160496444995</v>
       </c>
       <c r="AO3">
-        <v>55.06143708069439</v>
+        <v>18.87146364271179</v>
       </c>
       <c r="AP3">
-        <v>727.7125658781429</v>
+        <v>833.0761109020865</v>
       </c>
       <c r="AQ3">
-        <v>49.20128110633151</v>
+        <v>56.8624218172268</v>
       </c>
       <c r="AR3">
-        <v>13.91184566061243</v>
+        <v>42.49126534466478</v>
       </c>
       <c r="AS3">
-        <v>4.614283272074537</v>
+        <v>5.532847388817125</v>
       </c>
       <c r="AT3">
-        <v>2.79180960055255</v>
+        <v>4.409734222159909</v>
       </c>
       <c r="AU3">
-        <v>56.26481822202563</v>
+        <v>61.15165496520426</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -851,127 +857,118 @@
         </is>
       </c>
       <c r="B4">
-        <v>169.8064010692379</v>
+        <v>197.0956246626072</v>
       </c>
       <c r="C4">
-        <v>43.65199646531591</v>
+        <v>64.96838969859913</v>
       </c>
       <c r="D4">
-        <v>5725.178745227417</v>
+        <v>6290.950307160764</v>
       </c>
       <c r="E4">
-        <v>71.25180257192504</v>
+        <v>111.966521666951</v>
       </c>
       <c r="F4">
-        <v>157.4726792852417</v>
+        <v>188.6933283989782</v>
       </c>
       <c r="G4">
-        <v>3.165660261448537</v>
+        <v>4.564767515923567</v>
       </c>
       <c r="H4">
-        <v>26.06852641528153</v>
+        <v>29.69960823616791</v>
       </c>
       <c r="I4">
-        <v>84.77904721401977</v>
+        <v>93.06295848497935</v>
       </c>
       <c r="J4">
-        <v>12.3110447320021</v>
+        <v>21.25143268236806</v>
       </c>
       <c r="K4">
-        <v>3.592267206884112E-15</v>
+        <v>1.607147300057082E-15</v>
       </c>
       <c r="L4">
-        <v>3782.277518488781</v>
+        <v>4208.24854618037</v>
       </c>
       <c r="M4">
-        <v>898.6154481739363</v>
+        <v>1038.440376865599</v>
       </c>
       <c r="N4">
-        <v>965.3614312497921</v>
+        <v>1033.791984345875</v>
       </c>
       <c r="O4">
-        <v>61.95763093029097</v>
+        <v>80.06745118879131</v>
       </c>
       <c r="P4">
-        <v>9.68390660008944</v>
-      </c>
-      <c r="Q4">
-        <v>0.001101146161570692</v>
+        <v>16.88203164075242</v>
       </c>
       <c r="S4">
-        <v>0.3587623593598979</v>
+        <v>1.5249314861657</v>
       </c>
       <c r="T4">
-        <v>1.220564166059237</v>
+        <v>1.296973783782932</v>
       </c>
       <c r="U4">
-        <v>0.8978670076726343</v>
+        <v>0.7625222888636732</v>
       </c>
       <c r="V4">
-        <v>63.03933504483657</v>
+        <v>68.35107793773491</v>
       </c>
       <c r="W4">
-        <v>86.19288638423185</v>
+        <v>106.6937784263088</v>
       </c>
       <c r="Z4">
-        <v>1.175378078923063E-14</v>
+        <v>1.035314297357543E-14</v>
       </c>
       <c r="AA4">
-        <v>1.964530800357446</v>
+        <v>3.116689491753818</v>
       </c>
       <c r="AB4">
-        <v>1.315701619778346</v>
+        <v>1.08698376761204</v>
       </c>
       <c r="AC4">
-        <v>8.872686227724777E-17</v>
-      </c>
-      <c r="AE4">
-        <v>0.1920357684463735</v>
+        <v>-2.791083999132521E-17</v>
       </c>
       <c r="AF4">
-        <v>25.13764844840546</v>
-      </c>
-      <c r="AG4">
-        <v>46.61364158392152</v>
+        <v>29.69960823616791</v>
       </c>
       <c r="AH4">
-        <v>1397.370823905824</v>
+        <v>1594.054122235565</v>
       </c>
       <c r="AJ4">
-        <v>33.18155770333667</v>
+        <v>32.65652267560927</v>
       </c>
       <c r="AK4">
-        <v>960.2376345944492</v>
+        <v>1235.876068481306</v>
       </c>
       <c r="AL4">
-        <v>157.4943072988632</v>
+        <v>170.7848889459507</v>
       </c>
       <c r="AM4">
-        <v>759.1673482805024</v>
+        <v>877.8568757493791</v>
       </c>
       <c r="AN4">
-        <v>29.44907168162823</v>
+        <v>27.89379567334411</v>
       </c>
       <c r="AO4">
-        <v>53.76942589788913</v>
+        <v>22.04253596601929</v>
       </c>
       <c r="AP4">
-        <v>754.9617747688144</v>
+        <v>811.1143161471008</v>
       </c>
       <c r="AQ4">
-        <v>6.751457685831065</v>
+        <v>6.628315286624204</v>
       </c>
       <c r="AR4">
-        <v>61.93428067751761</v>
+        <v>157.7655126349605</v>
       </c>
       <c r="AS4">
-        <v>39.08398145965904</v>
+        <v>7.083095622292342</v>
       </c>
       <c r="AT4">
-        <v>6.886431356723794</v>
+        <v>7.566068195237158</v>
       </c>
       <c r="AU4">
-        <v>22.36866533173394</v>
+        <v>6.535762545961402</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -984,121 +981,118 @@
         </is>
       </c>
       <c r="B5">
-        <v>416.3934126918624</v>
+        <v>413.4902098740756</v>
       </c>
       <c r="C5">
-        <v>5.99143797735054</v>
+        <v>68.51538084924498</v>
       </c>
       <c r="D5">
-        <v>5609.384104910445</v>
+        <v>6538.38245446515</v>
       </c>
       <c r="E5">
-        <v>172.4607249238737</v>
+        <v>209.6835760039729</v>
       </c>
       <c r="F5">
-        <v>405.2196854783878</v>
+        <v>374.0262391340003</v>
       </c>
       <c r="G5">
-        <v>9.822606410499439</v>
+        <v>12.60067356468474</v>
       </c>
       <c r="H5">
-        <v>9.861166111030585</v>
+        <v>9.114944438413008</v>
       </c>
       <c r="I5">
-        <v>1.455961399787911</v>
+        <v>94.22497703493447</v>
       </c>
       <c r="J5">
-        <v>23.02330549545078</v>
+        <v>40.00470122262512</v>
       </c>
       <c r="K5">
-        <v>7.646326556777328E-15</v>
+        <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>2862.743723047834</v>
+        <v>3630.728121019108</v>
       </c>
       <c r="M5">
-        <v>819.2357610266417</v>
+        <v>1220.800751640906</v>
       </c>
       <c r="N5">
-        <v>1505.172164946129</v>
+        <v>1657.196671974522</v>
       </c>
       <c r="O5">
-        <v>155.0696332902088</v>
+        <v>165.9859248676359</v>
       </c>
       <c r="P5">
-        <v>7.948240073520872</v>
+        <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>0.003299789612865642</v>
+        <v>0.0361522857166593</v>
       </c>
       <c r="T5">
-        <v>0.7597212194143602</v>
+        <v>1.522509883925305</v>
       </c>
       <c r="U5">
-        <v>0.5301664661050942</v>
+        <v>1.433229457110054</v>
       </c>
       <c r="V5">
-        <v>234.6221040717803</v>
+        <v>206.7065011580776</v>
       </c>
       <c r="W5">
-        <v>139.4893365609659</v>
+        <v>160.9533127470356</v>
       </c>
       <c r="Z5">
-        <v>1.527710007243002E-14</v>
+        <v>-3.2409610753601E-14</v>
       </c>
       <c r="AA5">
-        <v>7.168280221227285</v>
+        <v>10.4491728470465</v>
       </c>
       <c r="AB5">
-        <v>10.52755684724459</v>
+        <v>9.365043096257695</v>
       </c>
       <c r="AC5">
-        <v>1.909637509053752E-15</v>
+        <v>2.616779913327972E-16</v>
       </c>
       <c r="AE5">
-        <v>1.351484528409652</v>
+        <v>1.127458624884201</v>
       </c>
       <c r="AF5">
-        <v>18.9838641581631</v>
-      </c>
-      <c r="AG5">
-        <v>4.816122862275973E-15</v>
+        <v>12.04646692999412</v>
       </c>
       <c r="AH5">
-        <v>1272.091183954896</v>
+        <v>1429.207058482918</v>
       </c>
       <c r="AJ5">
-        <v>53.5039084413973</v>
+        <v>42.11441806601042</v>
       </c>
       <c r="AK5">
-        <v>658.593011596852</v>
+        <v>1112.848383460228</v>
       </c>
       <c r="AL5">
-        <v>85.75401409891448</v>
+        <v>125.2594172616548</v>
       </c>
       <c r="AM5">
-        <v>13.96126618792321</v>
+        <v>72.64713520474027</v>
       </c>
       <c r="AN5">
-        <v>28.25593161153094</v>
+        <v>34.37591445852534</v>
       </c>
       <c r="AO5">
-        <v>206.9362295933304</v>
+        <v>452.2476249890937</v>
       </c>
       <c r="AP5">
-        <v>467.1109595705419</v>
+        <v>648.4116849890066</v>
       </c>
       <c r="AQ5">
-        <v>16.53556858545513</v>
+        <v>12.78723930509401</v>
       </c>
       <c r="AR5">
-        <v>53.85009097270819</v>
+        <v>64.83804046233173</v>
       </c>
       <c r="AS5">
-        <v>33.46432792097434</v>
+        <v>35.22086107921929</v>
       </c>
       <c r="AU5">
-        <v>129.6878218714913</v>
+        <v>205.6153018129811</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1111,133 +1105,127 @@
         </is>
       </c>
       <c r="B6">
-        <v>320.2118049689144</v>
+        <v>350.8147021768041</v>
       </c>
       <c r="C6">
-        <v>34.33856224325772</v>
+        <v>32.55126664973344</v>
       </c>
       <c r="D6">
-        <v>5365.508380461019</v>
+        <v>5977.657846673373</v>
       </c>
       <c r="E6">
-        <v>83.33969335807183</v>
+        <v>103.625537640387</v>
       </c>
       <c r="F6">
-        <v>294.998714320504</v>
+        <v>328.500579683218</v>
       </c>
       <c r="G6">
-        <v>15.70256886760692</v>
+        <v>17.51428034651915</v>
       </c>
       <c r="H6">
-        <v>9.845618549563504</v>
+        <v>5.773593827775013</v>
       </c>
       <c r="I6">
-        <v>187.5633839444355</v>
+        <v>209.9288514485036</v>
       </c>
       <c r="J6">
-        <v>29.91768848859997</v>
+        <v>28.71299786465505</v>
       </c>
       <c r="K6">
-        <v>3.311015979150592E-15</v>
+        <v>9.273740571928618E-15</v>
       </c>
       <c r="L6">
-        <v>3750.143036022394</v>
+        <v>4183.808065748052</v>
       </c>
       <c r="M6">
-        <v>577.3547533346373</v>
+        <v>638.8528061164935</v>
       </c>
       <c r="N6">
-        <v>971.048395873335</v>
+        <v>1052.935800706844</v>
       </c>
       <c r="O6">
-        <v>46.02889006016961</v>
+        <v>72.28900907220351</v>
       </c>
       <c r="P6">
-        <v>13.95828267013427</v>
+        <v>11.2406980760256</v>
       </c>
       <c r="Q6">
-        <v>4.408949130575656</v>
-      </c>
-      <c r="R6">
-        <v>0.2392146017699115</v>
+        <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>8.601605241006173</v>
+        <v>7.526826259557396</v>
       </c>
       <c r="T6">
-        <v>9.945061131264275</v>
+        <v>12.0812979966611</v>
       </c>
       <c r="U6">
-        <v>6.360471944077084</v>
+        <v>7.419998755367478</v>
       </c>
       <c r="V6">
-        <v>109.4936022677715</v>
+        <v>109.5133235760338</v>
       </c>
       <c r="W6">
-        <v>140.7074450345173</v>
+        <v>166.8159015987111</v>
       </c>
       <c r="Z6">
-        <v>2.005890717487678E-14</v>
+        <v>1.996489827249782E-14</v>
       </c>
       <c r="AA6">
-        <v>12.91350257281633</v>
+        <v>15.17767611440873</v>
       </c>
       <c r="AB6">
-        <v>1.808872991421456</v>
+        <v>1.883380391419592</v>
       </c>
       <c r="AC6">
-        <v>2.136970633864963E-16</v>
+        <v>-2.021347908133619E-16</v>
       </c>
       <c r="AD6">
-        <v>0.3205167475609768</v>
-      </c>
-      <c r="AE6">
-        <v>0.4695450910594603</v>
+        <v>0.1351699846782949</v>
       </c>
       <c r="AF6">
-        <v>24.74139321322372</v>
+        <v>10.91802824333649</v>
       </c>
       <c r="AG6">
-        <v>0.05929532381892133</v>
+        <v>0.1804582074521651</v>
       </c>
       <c r="AH6">
-        <v>2038.514846017395</v>
+        <v>2250.765603366898</v>
       </c>
       <c r="AJ6">
-        <v>42.32926842335591</v>
+        <v>45.79033585326558</v>
       </c>
       <c r="AK6">
-        <v>612.8537552742615</v>
+        <v>650.8421110089175</v>
       </c>
       <c r="AL6">
-        <v>145.9426845585965</v>
+        <v>148.861337306761</v>
       </c>
       <c r="AM6">
-        <v>612.3468730539105</v>
+        <v>808.6973780015492</v>
       </c>
       <c r="AN6">
-        <v>30.40439614783967</v>
+        <v>32.10897424745097</v>
       </c>
       <c r="AO6">
-        <v>37.93062807982367</v>
+        <v>20.71018340332767</v>
       </c>
       <c r="AP6">
-        <v>447.8478569364271</v>
+        <v>493.7454685494223</v>
       </c>
       <c r="AQ6">
-        <v>35.83924752627318</v>
+        <v>40.43931626826672</v>
       </c>
       <c r="AR6">
-        <v>12.59225242294288</v>
+        <v>23.96999779371208</v>
       </c>
       <c r="AS6">
-        <v>9.103132743219202</v>
+        <v>9.211068043877695</v>
       </c>
       <c r="AT6">
-        <v>0.9002602233814221</v>
+        <v>1.196950380553695</v>
       </c>
       <c r="AU6">
-        <v>30.42467224475259</v>
+        <v>34.80163155365587</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1250,124 +1238,121 @@
         </is>
       </c>
       <c r="B7">
-        <v>240.7789668141871</v>
+        <v>291.0827894269316</v>
       </c>
       <c r="C7">
-        <v>60.21665932345998</v>
+        <v>65.56210761528904</v>
       </c>
       <c r="D7">
-        <v>5305.907318049677</v>
+        <v>6006.871880705765</v>
       </c>
       <c r="E7">
-        <v>130.9452868118297</v>
+        <v>183.8245219388074</v>
       </c>
       <c r="F7">
-        <v>236.4749385590393</v>
+        <v>279.9300641248758</v>
       </c>
       <c r="G7">
-        <v>7.314676292778087</v>
+        <v>8.700331850927155</v>
       </c>
       <c r="H7">
-        <v>32.70434582889016</v>
+        <v>23.18794221746646</v>
       </c>
       <c r="I7">
-        <v>169.8700722125939</v>
+        <v>172.3529954373212</v>
       </c>
       <c r="J7">
-        <v>43.89522739737586</v>
+        <v>47.41956671979594</v>
       </c>
       <c r="K7">
-        <v>4.813000105937716E-15</v>
+        <v>-4.059111639711814E-15</v>
       </c>
       <c r="L7">
-        <v>3634.248306199715</v>
+        <v>4141.197897806307</v>
       </c>
       <c r="M7">
-        <v>723.8560611853402</v>
+        <v>780.9963896051678</v>
       </c>
       <c r="N7">
-        <v>908.0545850333961</v>
+        <v>969.3430140374692</v>
       </c>
       <c r="O7">
-        <v>57.79428365868996</v>
+        <v>96.75303008437479</v>
       </c>
       <c r="P7">
-        <v>3.353264327740249</v>
+        <v>6.844935925762263</v>
       </c>
       <c r="S7">
-        <v>33.15140322692547</v>
+        <v>39.79664254374238</v>
       </c>
       <c r="T7">
-        <v>8.397532578875172</v>
+        <v>10.83914604800249</v>
       </c>
       <c r="U7">
-        <v>3.384309744418224</v>
+        <v>3.902434337328899</v>
       </c>
       <c r="V7">
-        <v>84.33489137763016</v>
+        <v>91.62737201914183</v>
       </c>
       <c r="W7">
-        <v>130.4881796523518</v>
+        <v>159.0699114954697</v>
       </c>
       <c r="Z7">
-        <v>-1.343279545686665E-14</v>
+        <v>9.603639814134203E-15</v>
       </c>
       <c r="AA7">
-        <v>5.594918282850294</v>
+        <v>6.882694364662771</v>
       </c>
       <c r="AB7">
-        <v>1.075836400153244</v>
+        <v>0.8602998042679143</v>
       </c>
       <c r="AC7">
-        <v>-1.290091482954613E-16</v>
-      </c>
-      <c r="AE7">
-        <v>50.83445850914205</v>
+        <v>1.523394344702399E-16</v>
       </c>
       <c r="AF7">
-        <v>32.70434582889016</v>
+        <v>47.37440303115352</v>
       </c>
       <c r="AG7">
-        <v>0.0303951367781155</v>
+        <v>0.0986775719198664</v>
       </c>
       <c r="AH7">
-        <v>1796.362865652095</v>
+        <v>2000.365757216281</v>
       </c>
       <c r="AJ7">
-        <v>36.99805910895456</v>
+        <v>38.98415356922504</v>
       </c>
       <c r="AK7">
-        <v>673.9450833755237</v>
+        <v>710.9989905256232</v>
       </c>
       <c r="AL7">
-        <v>148.0966547833308</v>
+        <v>155.7119877016085</v>
       </c>
       <c r="AM7">
-        <v>783.4954930129293</v>
+        <v>1087.015919304921</v>
       </c>
       <c r="AN7">
-        <v>34.65816961605878</v>
+        <v>33.15141471334117</v>
       </c>
       <c r="AO7">
-        <v>28.69970654924324</v>
+        <v>14.79950112779897</v>
       </c>
       <c r="AP7">
-        <v>546.8778262833462</v>
+        <v>605.6769086159679</v>
       </c>
       <c r="AQ7">
-        <v>54.32082580318092</v>
+        <v>61.09073503603675</v>
       </c>
       <c r="AR7">
-        <v>26.22606871230003</v>
+        <v>26.38271995327089</v>
       </c>
       <c r="AS7">
-        <v>3.013583560574984</v>
+        <v>3.924561212253352</v>
       </c>
       <c r="AT7">
-        <v>0.1038730127767483</v>
+        <v>0.08931485835975785</v>
       </c>
       <c r="AU7">
-        <v>61.74192121352343</v>
+        <v>64.70646856723832</v>
       </c>
       <c r="AV7">
         <v>1</v>
@@ -1380,109 +1365,109 @@
         </is>
       </c>
       <c r="B8">
-        <v>8328.623806946987</v>
+        <v>9021.561814742507</v>
       </c>
       <c r="C8">
-        <v>922.5491187963864</v>
+        <v>1003.371916347531</v>
       </c>
       <c r="D8">
-        <v>2372.308437906705</v>
+        <v>2362.819582725343</v>
       </c>
       <c r="E8">
-        <v>1442.628285151825</v>
+        <v>1695.772933258678</v>
       </c>
       <c r="F8">
-        <v>8141.057707744824</v>
+        <v>8818.093409888021</v>
       </c>
       <c r="G8">
-        <v>187.5660992021639</v>
+        <v>203.4684048544846</v>
       </c>
       <c r="I8">
-        <v>813.1475211762837</v>
+        <v>890.0134890431743</v>
       </c>
       <c r="J8">
-        <v>108.1222277926444</v>
+        <v>111.897395864859</v>
       </c>
       <c r="K8">
-        <v>1.279369827458352</v>
+        <v>1.46103143949791</v>
       </c>
       <c r="L8">
-        <v>1288.466423449235</v>
+        <v>1212.741071534276</v>
       </c>
       <c r="M8">
-        <v>18.79229684144322</v>
+        <v>17.18444441737943</v>
       </c>
       <c r="N8">
-        <v>1065.049717616026</v>
+        <v>1132.894066773688</v>
       </c>
       <c r="O8">
-        <v>532.1228890331223</v>
+        <v>662.5337091473554</v>
       </c>
       <c r="P8">
-        <v>459.8563450099872</v>
+        <v>603.0005718077252</v>
       </c>
       <c r="Q8">
-        <v>0.004455518238122473</v>
+        <v>0.00117491113314129</v>
       </c>
       <c r="R8">
-        <v>1.140091316332408</v>
+        <v>1.359412456008694</v>
       </c>
       <c r="S8">
-        <v>449.5045042741453</v>
+        <v>428.8780649364567</v>
       </c>
       <c r="T8">
-        <v>447.6080372285537</v>
+        <v>457.5150913560984</v>
       </c>
       <c r="U8">
-        <v>208.2172361974482</v>
+        <v>159.9617542132718</v>
       </c>
       <c r="V8">
-        <v>1164.212709481437</v>
+        <v>1288.927598841336</v>
       </c>
       <c r="W8">
-        <v>1653.10405043821</v>
+        <v>1886.389658119943</v>
       </c>
       <c r="X8">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="Y8">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Z8">
-        <v>119.546345915171</v>
+        <v>160.4623832034374</v>
       </c>
       <c r="AA8">
-        <v>97.61441588122374</v>
+        <v>112.316207423073</v>
       </c>
       <c r="AB8">
-        <v>89.95168332094012</v>
+        <v>91.15219743141159</v>
       </c>
       <c r="AH8">
-        <v>162.7477208364708</v>
+        <v>138.853704719445</v>
       </c>
       <c r="AI8">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AJ8">
-        <v>6.100514684435994</v>
+        <v>4.808966761976296</v>
       </c>
       <c r="AK8">
-        <v>363.3375090669293</v>
+        <v>419.135125568129</v>
       </c>
       <c r="AL8">
-        <v>134.2162605294725</v>
+        <v>96.11884881672688</v>
       </c>
       <c r="AM8">
-        <v>25.43321615666796</v>
+        <v>8.40881313984889</v>
       </c>
       <c r="AN8">
-        <v>12.19455021727776</v>
+        <v>6.995374812431117</v>
       </c>
       <c r="AO8">
-        <v>154.9893470603973</v>
+        <v>70.91648566067794</v>
       </c>
       <c r="AU8">
-        <v>18.79229684144322</v>
+        <v>17.18444441737943</v>
       </c>
       <c r="AV8">
         <v>1</v>
@@ -1495,133 +1480,130 @@
         </is>
       </c>
       <c r="B9">
-        <v>507.3762625976088</v>
+        <v>545.7378921718523</v>
       </c>
       <c r="C9">
-        <v>126.8693729554598</v>
+        <v>132.6241103282866</v>
       </c>
       <c r="D9">
-        <v>5736.585227237649</v>
+        <v>6532.525897978622</v>
       </c>
       <c r="E9">
-        <v>310.4166384766984</v>
+        <v>349.4722130529491</v>
       </c>
       <c r="F9">
-        <v>471.7497120885447</v>
+        <v>474.6869633972992</v>
       </c>
       <c r="G9">
-        <v>45.70886048677699</v>
+        <v>53.01504975124379</v>
       </c>
       <c r="H9">
-        <v>7.56953419858269</v>
+        <v>0.5835266396125148</v>
       </c>
       <c r="I9">
-        <v>121.0780203340596</v>
+        <v>138.5467381005542</v>
       </c>
       <c r="J9">
-        <v>83.77355046538281</v>
+        <v>89.8292738740452</v>
       </c>
       <c r="K9">
-        <v>8.312719512958909E-15</v>
+        <v>8.430700958862792E-15</v>
       </c>
       <c r="L9">
-        <v>2841.011115211721</v>
+        <v>3279.145877178284</v>
       </c>
       <c r="M9">
-        <v>1810.186623095641</v>
+        <v>2089.162812077871</v>
       </c>
       <c r="N9">
-        <v>993.1319549208769</v>
+        <v>1113.784550225981</v>
       </c>
       <c r="O9">
-        <v>151.9388707669528</v>
+        <v>206.8651069696682</v>
       </c>
       <c r="P9">
-        <v>90.45885884748978</v>
+        <v>94.2962349609916</v>
       </c>
       <c r="Q9">
-        <v>0.4113173667996252</v>
-      </c>
-      <c r="R9">
-        <v>1.061057371096587</v>
+        <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>48.28903441336706</v>
+        <v>35.6182305816803</v>
       </c>
       <c r="T9">
-        <v>48.96535075875308</v>
+        <v>58.23257376523413</v>
       </c>
       <c r="U9">
-        <v>35.26048032425083</v>
+        <v>44.80726372705811</v>
       </c>
       <c r="V9">
-        <v>245.2427682832981</v>
+        <v>230.4731929936596</v>
       </c>
       <c r="W9">
-        <v>132.0359066135322</v>
+        <v>156.8528275566048</v>
       </c>
       <c r="Z9">
-        <v>-2.056486203975163E-14</v>
+        <v>-2.05935471124951E-14</v>
       </c>
       <c r="AA9">
-        <v>17.75234099658151</v>
+        <v>17.35673148568832</v>
       </c>
       <c r="AB9">
-        <v>26.55734604273478</v>
+        <v>35.37594785442694</v>
       </c>
       <c r="AC9">
-        <v>-3.148636087047191E-16</v>
+        <v>6.629936592600439E-17</v>
       </c>
       <c r="AD9">
-        <v>0.0005174751895457067</v>
+        <v>7.30219373921617E-05</v>
       </c>
       <c r="AE9">
-        <v>7.775627508696815</v>
+        <v>1.302203162690968</v>
       </c>
       <c r="AF9">
-        <v>14.24555839106512</v>
+        <v>0.5835266396125148</v>
       </c>
       <c r="AG9">
-        <v>0.04481679917041134</v>
+        <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1738.104518406555</v>
+        <v>1932.526450400248</v>
       </c>
       <c r="AJ9">
-        <v>183.2959620711698</v>
+        <v>190.7531598062954</v>
       </c>
       <c r="AK9">
-        <v>478.539298659045</v>
+        <v>540.7165715004402</v>
       </c>
       <c r="AL9">
-        <v>101.107133658624</v>
+        <v>105.615641492929</v>
       </c>
       <c r="AM9">
-        <v>105.9493744362727</v>
+        <v>122.9130624559105</v>
       </c>
       <c r="AN9">
-        <v>20.50982058204816</v>
+        <v>21.23644201030928</v>
       </c>
       <c r="AO9">
-        <v>25.4558097559976</v>
+        <v>22.88135181265783</v>
       </c>
       <c r="AP9">
-        <v>1329.635641900516</v>
+        <v>1485.060486709982</v>
       </c>
       <c r="AQ9">
-        <v>130.6195937516576</v>
+        <v>154.4604296223639</v>
       </c>
       <c r="AR9">
-        <v>18.77149715547821</v>
+        <v>7.486446280991736</v>
       </c>
       <c r="AS9">
-        <v>31.81168703192747</v>
+        <v>34.15310754414983</v>
       </c>
       <c r="AT9">
-        <v>25.76849922351921</v>
+        <v>27.03334577114428</v>
       </c>
       <c r="AU9">
-        <v>203.9346700360793</v>
+        <v>221.7188168585555</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1634,133 +1616,133 @@
         </is>
       </c>
       <c r="B10">
-        <v>695.6147848932703</v>
+        <v>842.1912774017301</v>
       </c>
       <c r="C10">
-        <v>286.2809218384766</v>
+        <v>289.7960718981939</v>
       </c>
       <c r="D10">
-        <v>6482.011595172992</v>
+        <v>7779.616688941662</v>
       </c>
       <c r="E10">
-        <v>252.6878592869401</v>
+        <v>348.589878111765</v>
       </c>
       <c r="F10">
-        <v>626.5241840068309</v>
+        <v>802.0819527194764</v>
       </c>
       <c r="G10">
-        <v>36.45301575668743</v>
+        <v>40.13066415239069</v>
       </c>
       <c r="H10">
-        <v>2.502457239288276</v>
+        <v>6.581133333333334</v>
       </c>
       <c r="I10">
-        <v>304.1052776154792</v>
+        <v>300.7929783136822</v>
       </c>
       <c r="J10">
-        <v>60.02081263383938</v>
+        <v>56.95789947937525</v>
       </c>
       <c r="K10">
-        <v>4.561377644529237E-15</v>
+        <v>-5.526165079581177E-15</v>
       </c>
       <c r="L10">
-        <v>3556.520842866552</v>
+        <v>4154.19768983191</v>
       </c>
       <c r="M10">
-        <v>1869.575073742293</v>
+        <v>2482.627966682026</v>
       </c>
       <c r="N10">
-        <v>818.365090792985</v>
+        <v>838.8127846930881</v>
       </c>
       <c r="O10">
-        <v>141.3029443163896</v>
+        <v>222.1371673508843</v>
       </c>
       <c r="P10">
-        <v>10.53771403235613</v>
+        <v>8.216045186628255</v>
       </c>
       <c r="Q10">
-        <v>1.401853323632016</v>
+        <v>0.1186472541760872</v>
       </c>
       <c r="R10">
-        <v>186.3840153070749</v>
+        <v>203.0695822454308</v>
       </c>
       <c r="S10">
-        <v>37.80007029652346</v>
+        <v>53.72012190240643</v>
       </c>
       <c r="T10">
-        <v>56.64805508776587</v>
+        <v>67.41809940752637</v>
       </c>
       <c r="U10">
-        <v>135.0471612604007</v>
+        <v>149.0841759486314</v>
       </c>
       <c r="V10">
-        <v>207.5363897094693</v>
+        <v>273.7698316520127</v>
       </c>
       <c r="W10">
-        <v>183.7094479592038</v>
+        <v>215.2670824283694</v>
       </c>
       <c r="Z10">
-        <v>1.650110869269097E-14</v>
+        <v>-1.674077104212465E-14</v>
       </c>
       <c r="AA10">
-        <v>17.05873351776589</v>
+        <v>20.96008654553387</v>
       </c>
       <c r="AB10">
-        <v>15.0895830861476</v>
+        <v>14.39772070242397</v>
       </c>
       <c r="AC10">
-        <v>8.329647284259509E-16</v>
+        <v>-2.433365533425001E-16</v>
       </c>
       <c r="AD10">
-        <v>2.229225012592646</v>
+        <v>40.04352829734064</v>
       </c>
       <c r="AE10">
-        <v>108.1275429874452</v>
+        <v>114.3676557073837</v>
       </c>
       <c r="AF10">
-        <v>12.50280995054156</v>
+        <v>19.45737962485965</v>
       </c>
       <c r="AG10">
-        <v>0.6291305394070994</v>
+        <v>1.470845643041063</v>
       </c>
       <c r="AH10">
-        <v>2280.858801921447</v>
+        <v>2677.950561169912</v>
       </c>
       <c r="AJ10">
-        <v>77.64461039349587</v>
+        <v>74.38103382072444</v>
       </c>
       <c r="AK10">
-        <v>516.228838944625</v>
+        <v>541.6088506558663</v>
       </c>
       <c r="AL10">
-        <v>82.92579420883513</v>
+        <v>86.48370835929539</v>
       </c>
       <c r="AM10">
-        <v>19.63305090779637</v>
+        <v>36.55220325189012</v>
       </c>
       <c r="AN10">
-        <v>35.86680379746835</v>
+        <v>34.2899358226371</v>
       </c>
       <c r="AO10">
-        <v>220.0308888355437</v>
+        <v>268.4811393475919</v>
       </c>
       <c r="AP10">
-        <v>1571.615962912555</v>
+        <v>1866.184977532371</v>
       </c>
       <c r="AQ10">
-        <v>157.3563937007874</v>
+        <v>167.1408913344304</v>
       </c>
       <c r="AR10">
-        <v>47.95332955954704</v>
+        <v>52.32232836905195</v>
       </c>
       <c r="AS10">
-        <v>11.8795743276687</v>
+        <v>23.12881464824928</v>
       </c>
       <c r="AT10">
-        <v>33.16724274919875</v>
+        <v>7.992159680439119</v>
       </c>
       <c r="AU10">
-        <v>135.7457130659772</v>
+        <v>187.9808272846278</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1773,127 +1755,130 @@
         </is>
       </c>
       <c r="B11">
-        <v>237.892997943888</v>
+        <v>271.3840453074433</v>
       </c>
       <c r="C11">
-        <v>44.68243298969072</v>
+        <v>48.3931805909126</v>
       </c>
       <c r="D11">
-        <v>5735.313998647029</v>
+        <v>6380.392780884303</v>
       </c>
       <c r="E11">
-        <v>59.25458393113386</v>
+        <v>92.96760541191735</v>
       </c>
       <c r="F11">
-        <v>224.7458281563605</v>
+        <v>253.4598772169168</v>
       </c>
       <c r="G11">
-        <v>3.010067199979511</v>
+        <v>4.678517422434368</v>
       </c>
       <c r="H11">
-        <v>8.483298409984247</v>
+        <v>13.64586692122755</v>
       </c>
       <c r="I11">
-        <v>189.9924887192601</v>
+        <v>209.4850869304556</v>
       </c>
       <c r="J11">
-        <v>34.54514430215885</v>
+        <v>37.32285591928192</v>
       </c>
       <c r="K11">
-        <v>5.671131291420126E-15</v>
+        <v>1.073216045359242E-14</v>
       </c>
       <c r="L11">
-        <v>4114.270795271736</v>
+        <v>4648.701299174356</v>
       </c>
       <c r="M11">
-        <v>512.0713295467718</v>
+        <v>576.3831793276677</v>
       </c>
       <c r="N11">
-        <v>956.1007177615562</v>
+        <v>1039.309296363591</v>
       </c>
       <c r="O11">
-        <v>36.57702042182792</v>
+        <v>72.99974335281181</v>
       </c>
       <c r="P11">
-        <v>19.20824883294829</v>
+        <v>9.079408226479135</v>
+      </c>
+      <c r="Q11">
+        <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>3.182625504077521</v>
+        <v>2.932098995410381</v>
       </c>
       <c r="T11">
-        <v>0.8864803035375516</v>
+        <v>1.161711366856404</v>
       </c>
       <c r="U11">
-        <v>3.908154616303544</v>
+        <v>4.840383921172424</v>
       </c>
       <c r="V11">
-        <v>74.12000271591526</v>
+        <v>82.05098882110903</v>
       </c>
       <c r="W11">
-        <v>117.0279663630643</v>
+        <v>142.0566528246388</v>
       </c>
       <c r="Z11">
-        <v>7.648838490600184E-15</v>
+        <v>4.667283975587595E-16</v>
       </c>
       <c r="AA11">
-        <v>1.60589765189007</v>
+        <v>3.283239521752231</v>
       </c>
       <c r="AB11">
-        <v>1.757460448932458</v>
+        <v>1.949293780337517</v>
       </c>
       <c r="AC11">
-        <v>2.065030958857157E-17</v>
+        <v>1.022648555459479E-16</v>
       </c>
       <c r="AD11">
-        <v>9.215029407883575</v>
+        <v>4.272685064935065</v>
       </c>
       <c r="AE11">
-        <v>0.8880009852660793</v>
+        <v>0.1282782123186037</v>
       </c>
       <c r="AF11">
-        <v>35.99151152860802</v>
+        <v>39.36904774649395</v>
       </c>
       <c r="AG11">
-        <v>0.1193384102808187</v>
+        <v>0.8486997964094021</v>
       </c>
       <c r="AH11">
-        <v>1708.612725710296</v>
+        <v>1917.480914938862</v>
       </c>
       <c r="AJ11">
-        <v>32.75660272444755</v>
+        <v>35.57198992090712</v>
       </c>
       <c r="AK11">
-        <v>697.4895116748989</v>
+        <v>790.3856025809274</v>
       </c>
       <c r="AL11">
-        <v>170.5083766460277</v>
+        <v>177.0625143272992</v>
       </c>
       <c r="AM11">
-        <v>1224.29431161032</v>
+        <v>1463.404233380704</v>
       </c>
       <c r="AN11">
-        <v>35.71234902896887</v>
+        <v>35.10222986111111</v>
       </c>
       <c r="AO11">
-        <v>50.18047759433902</v>
+        <v>47.50966262135946</v>
       </c>
       <c r="AP11">
-        <v>422.6357346334003</v>
+        <v>474.1814182334641</v>
       </c>
       <c r="AQ11">
-        <v>29.28558874419452</v>
+        <v>34.86353848617487</v>
       </c>
       <c r="AR11">
-        <v>3.644608612822298</v>
+        <v>21.19330543933054</v>
       </c>
       <c r="AS11">
-        <v>0.4636705613768397</v>
+        <v>1.05202759270869</v>
       </c>
       <c r="AT11">
-        <v>0.5440323865827015</v>
+        <v>0.2568273264275319</v>
       </c>
       <c r="AU11">
-        <v>8.435669108450977</v>
+        <v>15.98991570002732</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1906,133 +1891,133 @@
         </is>
       </c>
       <c r="B12">
-        <v>401.3003411458333</v>
+        <v>471.1061763022324</v>
       </c>
       <c r="C12">
-        <v>84.73742657996118</v>
+        <v>95.94523588817876</v>
       </c>
       <c r="D12">
-        <v>5649.094768583954</v>
+        <v>6336.80887034861</v>
       </c>
       <c r="E12">
-        <v>216.7255998713403</v>
+        <v>276.8376930099113</v>
       </c>
       <c r="F12">
-        <v>365.4418425197322</v>
+        <v>429.8226617820846</v>
       </c>
       <c r="G12">
-        <v>28.309695604436</v>
+        <v>33.31708564153057</v>
       </c>
       <c r="H12">
-        <v>0.5137120289547137</v>
+        <v>0.7983256145350909</v>
       </c>
       <c r="I12">
-        <v>145.2884163623083</v>
+        <v>158.6983659491194</v>
       </c>
       <c r="J12">
-        <v>72.81031240756664</v>
+        <v>79.80534141646369</v>
       </c>
       <c r="K12">
-        <v>6.995114383095253E-15</v>
+        <v>6.706724382240743E-15</v>
       </c>
       <c r="L12">
-        <v>3331.5168645539</v>
+        <v>3773.589144505417</v>
       </c>
       <c r="M12">
-        <v>1404.506385473263</v>
+        <v>1555.481336717929</v>
       </c>
       <c r="N12">
-        <v>720.4192795717797</v>
+        <v>800.2877821363913</v>
       </c>
       <c r="O12">
-        <v>145.9890438018895</v>
+        <v>201.9386756019991</v>
       </c>
       <c r="P12">
-        <v>8.422994657163855</v>
+        <v>10.16855529318787</v>
       </c>
       <c r="Q12">
-        <v>0.9414283387404614</v>
+        <v>0.8076131687242798</v>
       </c>
       <c r="R12">
-        <v>6.204903737259343</v>
+        <v>8.656320998762794</v>
       </c>
       <c r="S12">
-        <v>20.60194078128936</v>
+        <v>20.36292619089226</v>
       </c>
       <c r="T12">
-        <v>36.40612586545417</v>
+        <v>43.37962820891119</v>
       </c>
       <c r="U12">
-        <v>38.20083844317679</v>
+        <v>46.65965869660025</v>
       </c>
       <c r="V12">
-        <v>135.1238270418668</v>
+        <v>147.3945575447854</v>
       </c>
       <c r="W12">
-        <v>123.2157023495776</v>
+        <v>146.0594726017296</v>
       </c>
       <c r="Z12">
-        <v>9.504843388874495E-15</v>
+        <v>1.171887676937133E-14</v>
       </c>
       <c r="AA12">
-        <v>10.26497872932795</v>
+        <v>11.95248037116346</v>
       </c>
       <c r="AB12">
-        <v>16.24920842411039</v>
+        <v>18.73349590373784</v>
       </c>
       <c r="AC12">
-        <v>2.285736873015653E-16</v>
+        <v>7.79019294734521E-17</v>
       </c>
       <c r="AD12">
-        <v>0.04178682336820537</v>
+        <v>0.1342105518876827</v>
       </c>
       <c r="AE12">
-        <v>1.331585689405407</v>
+        <v>1.778143255117469</v>
       </c>
       <c r="AF12">
-        <v>2.505081246516299</v>
+        <v>2.257711735249292</v>
       </c>
       <c r="AG12">
-        <v>0.1726096232665207</v>
+        <v>0.2541977994181236</v>
       </c>
       <c r="AH12">
-        <v>2374.824221519485</v>
+        <v>2641.514109957709</v>
       </c>
       <c r="AJ12">
-        <v>65.27318021260946</v>
+        <v>71.21413351100733</v>
       </c>
       <c r="AK12">
-        <v>529.8168154761905</v>
+        <v>613.7223436001248</v>
       </c>
       <c r="AL12">
-        <v>74.6037973273942</v>
+        <v>76.81353945154052</v>
       </c>
       <c r="AM12">
-        <v>16.47411006930427</v>
+        <v>31.96393883651415</v>
       </c>
       <c r="AN12">
-        <v>28.40502212347666</v>
+        <v>29.47392641874218</v>
       </c>
       <c r="AO12">
-        <v>32.46677179899119</v>
+        <v>22.00650663008598</v>
       </c>
       <c r="AP12">
-        <v>857.0910966497951</v>
+        <v>930.3908059626074</v>
       </c>
       <c r="AQ12">
-        <v>168.3869804547268</v>
+        <v>186.8084611137948</v>
       </c>
       <c r="AR12">
-        <v>192.6964808601134</v>
+        <v>225.5150443932917</v>
       </c>
       <c r="AS12">
-        <v>9.943244381211668</v>
+        <v>10.64599470085754</v>
       </c>
       <c r="AT12">
-        <v>1.27768298903341</v>
+        <v>1.939815386163185</v>
       </c>
       <c r="AU12">
-        <v>97.62967393561809</v>
+        <v>111.3117358384742</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2045,130 +2030,130 @@
         </is>
       </c>
       <c r="B13">
-        <v>1147.785671270718</v>
+        <v>1230.188966003367</v>
       </c>
       <c r="C13">
-        <v>282.3737324851715</v>
+        <v>293.5391090029762</v>
       </c>
       <c r="D13">
-        <v>6927.244836198987</v>
+        <v>7769.049949129853</v>
       </c>
       <c r="E13">
-        <v>320.7798364008183</v>
+        <v>367.1318367599396</v>
       </c>
       <c r="F13">
-        <v>1024.156940294393</v>
+        <v>1144.236526504298</v>
       </c>
       <c r="G13">
-        <v>57.70168205938349</v>
+        <v>73.50180744701069</v>
       </c>
       <c r="H13">
-        <v>0.3728515825590057</v>
+        <v>0.393982230876894</v>
       </c>
       <c r="I13">
-        <v>215.3715354742849</v>
+        <v>228.8921625358248</v>
       </c>
       <c r="J13">
-        <v>119.1857848260218</v>
+        <v>115.7405998400426</v>
       </c>
       <c r="K13">
-        <v>1.283591397838192E-14</v>
+        <v>7.858996950444529E-15</v>
       </c>
       <c r="L13">
-        <v>3015.472660118682</v>
+        <v>3444.195878709439</v>
       </c>
       <c r="M13">
-        <v>2795.351282372972</v>
+        <v>3004.133158579984</v>
       </c>
       <c r="N13">
-        <v>1144.816148886788</v>
+        <v>1225.397121937194</v>
       </c>
       <c r="O13">
-        <v>192.6627162832657</v>
+        <v>254.5577198059216</v>
       </c>
       <c r="P13">
-        <v>12.86053085927865</v>
+        <v>12.37283532135341</v>
       </c>
       <c r="Q13">
-        <v>2.347210684496674</v>
+        <v>2.915850730688935</v>
       </c>
       <c r="R13">
-        <v>24.96507945902755</v>
+        <v>14.27238282378778</v>
       </c>
       <c r="S13">
-        <v>52.28929173249214</v>
+        <v>50.13860420610362</v>
       </c>
       <c r="T13">
-        <v>125.9912776587272</v>
+        <v>151.9676602518023</v>
       </c>
       <c r="U13">
-        <v>151.9152412748629</v>
+        <v>171.2566247922596</v>
       </c>
       <c r="V13">
-        <v>377.6086250694877</v>
+        <v>404.1089236972443</v>
       </c>
       <c r="W13">
-        <v>285.9268989359094</v>
+        <v>343.5872743167828</v>
       </c>
       <c r="Z13">
-        <v>4.657544381953783E-14</v>
+        <v>5.109287186328324E-14</v>
       </c>
       <c r="AA13">
-        <v>22.06504252783565</v>
+        <v>22.2961704940849</v>
       </c>
       <c r="AB13">
-        <v>33.91090047873098</v>
+        <v>43.47169175789193</v>
       </c>
       <c r="AC13">
-        <v>4.899634757025876E-16</v>
+        <v>4.309890779637144E-16</v>
       </c>
       <c r="AD13">
-        <v>0.42674703803783</v>
-      </c>
-      <c r="AF13">
-        <v>73.51640203284198</v>
+        <v>0.9856260210222841</v>
+      </c>
+      <c r="AE13">
+        <v>2.517527938789705</v>
       </c>
       <c r="AG13">
-        <v>0.3189561270801816</v>
+        <v>0.2374112287562665</v>
       </c>
       <c r="AH13">
-        <v>2057.100109797297</v>
+        <v>2258.01662365231</v>
       </c>
       <c r="AJ13">
-        <v>42.56992791368829</v>
+        <v>45.17101965458096</v>
       </c>
       <c r="AK13">
-        <v>432.5167925094105</v>
+        <v>574.2971090655299</v>
       </c>
       <c r="AL13">
-        <v>96.44581277213352</v>
+        <v>108.0472319738427</v>
       </c>
       <c r="AM13">
-        <v>17.5832064294718</v>
+        <v>28.4537346688471</v>
       </c>
       <c r="AN13">
-        <v>24.91992659389576</v>
+        <v>24.75581553973903</v>
       </c>
       <c r="AO13">
-        <v>320.6281391971789</v>
+        <v>352.6543332958253</v>
       </c>
       <c r="AP13">
-        <v>2160.529673301794</v>
+        <v>2265.75252652989</v>
       </c>
       <c r="AQ13">
-        <v>152.760799743169</v>
+        <v>157.4463539664232</v>
       </c>
       <c r="AR13">
-        <v>171.4941774224253</v>
+        <v>166.4466392299107</v>
       </c>
       <c r="AS13">
-        <v>16.60919540229885</v>
+        <v>17.97994269340974</v>
       </c>
       <c r="AT13">
-        <v>5.913240850299889</v>
+        <v>28.79759762402376</v>
       </c>
       <c r="AU13">
-        <v>291.9490914848697</v>
+        <v>333.1987360890303</v>
       </c>
       <c r="AV13">
         <v>1</v>
@@ -2181,130 +2166,130 @@
         </is>
       </c>
       <c r="B14">
-        <v>1026.364694199955</v>
+        <v>1217.008394696597</v>
       </c>
       <c r="C14">
-        <v>273.1993715658546</v>
+        <v>307.8882896474652</v>
       </c>
       <c r="D14">
-        <v>7274.423909405655</v>
+        <v>8210.499215340811</v>
       </c>
       <c r="E14">
-        <v>416.8426244252089</v>
+        <v>469.5137284460254</v>
       </c>
       <c r="F14">
-        <v>947.4007357723577</v>
+        <v>1104.891272781036</v>
       </c>
       <c r="G14">
-        <v>58.45497800918727</v>
+        <v>70.1917068912965</v>
       </c>
       <c r="H14">
-        <v>3.308690012970168</v>
+        <v>2.645165488167103</v>
       </c>
       <c r="I14">
-        <v>196.6205459671978</v>
+        <v>235.2435950028662</v>
       </c>
       <c r="J14">
-        <v>89.32610850317725</v>
+        <v>92.71886059541902</v>
       </c>
       <c r="K14">
-        <v>9.834504714972322E-15</v>
+        <v>7.106812019524112E-15</v>
       </c>
       <c r="L14">
-        <v>2889.026651234568</v>
+        <v>3201.520331169863</v>
       </c>
       <c r="M14">
-        <v>3165.49310404292</v>
+        <v>3698.514659423688</v>
       </c>
       <c r="N14">
-        <v>1073.308394067797</v>
+        <v>1227.665646941396</v>
       </c>
       <c r="O14">
-        <v>230.3297557912364</v>
+        <v>274.5538544478901</v>
       </c>
       <c r="P14">
-        <v>70.90221734641197</v>
+        <v>93.29317893164614</v>
       </c>
       <c r="Q14">
-        <v>0.02023748723186925</v>
+        <v>1.248993123548431</v>
       </c>
       <c r="S14">
-        <v>68.69523175467754</v>
+        <v>79.29836408919209</v>
       </c>
       <c r="T14">
-        <v>83.36574358792689</v>
+        <v>113.4173302771076</v>
       </c>
       <c r="U14">
-        <v>170.8529941424949</v>
+        <v>202.6881136468232</v>
       </c>
       <c r="V14">
-        <v>360.8973318955746</v>
+        <v>391.0904795120989</v>
       </c>
       <c r="W14">
-        <v>275.3154758372192</v>
+        <v>328.808070616857</v>
       </c>
       <c r="Z14">
-        <v>1.037338577205924E-13</v>
+        <v>1.262599526867625E-13</v>
       </c>
       <c r="AA14">
-        <v>28.9146391685909</v>
+        <v>34.08089729263259</v>
       </c>
       <c r="AB14">
-        <v>21.61618978805395</v>
+        <v>27.67552092071268</v>
       </c>
       <c r="AC14">
-        <v>-6.274540888395503E-16</v>
+        <v>5.019076210876448E-16</v>
       </c>
       <c r="AD14">
-        <v>2.740952742524497</v>
+        <v>2.847533048873066</v>
       </c>
       <c r="AE14">
-        <v>1.697726301449113</v>
+        <v>7.192318955928982</v>
       </c>
       <c r="AF14">
-        <v>65.98862413139608</v>
+        <v>36.84581611942748</v>
       </c>
       <c r="AG14">
-        <v>0.6410769119238847</v>
+        <v>0.2694859428032323</v>
       </c>
       <c r="AH14">
-        <v>1765.137423282395</v>
+        <v>1936.623859782474</v>
       </c>
       <c r="AJ14">
-        <v>56.005424706789</v>
+        <v>60.23782392091884</v>
       </c>
       <c r="AK14">
-        <v>493.0941198803498</v>
+        <v>521.765263905949</v>
       </c>
       <c r="AL14">
-        <v>97.51527192706696</v>
+        <v>106.5576396496167</v>
       </c>
       <c r="AM14">
-        <v>22.26866880097219</v>
+        <v>52.49921122250679</v>
       </c>
       <c r="AN14">
-        <v>23.00823054981804</v>
+        <v>24.05868922444462</v>
       </c>
       <c r="AO14">
-        <v>355.0205600996696</v>
+        <v>374.5291086451645</v>
       </c>
       <c r="AP14">
-        <v>2290.73237023836</v>
+        <v>2873.440187058914</v>
       </c>
       <c r="AQ14">
-        <v>178.5977655850276</v>
+        <v>204.5406245584257</v>
       </c>
       <c r="AR14">
-        <v>171.4194615281321</v>
+        <v>201.3825451129178</v>
       </c>
       <c r="AS14">
-        <v>8.654194433926543</v>
+        <v>10.42676118218669</v>
       </c>
       <c r="AT14">
-        <v>1.757599100698142</v>
+        <v>45.66567917605976</v>
       </c>
       <c r="AU14">
-        <v>398.4784309921097</v>
+        <v>348.7305918461557</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2317,127 +2302,127 @@
         </is>
       </c>
       <c r="B15">
-        <v>319.9371388951353</v>
+        <v>357.7644610175856</v>
       </c>
       <c r="C15">
-        <v>68.30485296032924</v>
+        <v>64.30693912341638</v>
       </c>
       <c r="D15">
-        <v>4979.452091530481</v>
+        <v>5594.847214903799</v>
       </c>
       <c r="E15">
-        <v>53.33944761678157</v>
+        <v>91.20587493110777</v>
       </c>
       <c r="F15">
-        <v>282.475778079864</v>
+        <v>318.5760725663177</v>
       </c>
       <c r="G15">
-        <v>17.28735511048889</v>
+        <v>20.64240360568746</v>
       </c>
       <c r="H15">
-        <v>16.42423425518694</v>
+        <v>21.47982135996927</v>
       </c>
       <c r="I15">
-        <v>191.1904470828526</v>
+        <v>182.6611231723595</v>
       </c>
       <c r="J15">
-        <v>60.09536975783535</v>
+        <v>50.49470635537054</v>
       </c>
       <c r="K15">
-        <v>-9.223572620285608E-15</v>
+        <v>-5.915799143886172E-15</v>
       </c>
       <c r="L15">
-        <v>3153.195045222635</v>
+        <v>3665.14855503969</v>
       </c>
       <c r="M15">
-        <v>722.6766398305085</v>
+        <v>826.9730848214308</v>
       </c>
       <c r="N15">
-        <v>992.7112434908958</v>
+        <v>1000.978551705484</v>
       </c>
       <c r="O15">
-        <v>38.36231424449889</v>
+        <v>72.0438035688133</v>
       </c>
       <c r="P15">
-        <v>4.809115095367465</v>
+        <v>2.196935458167331</v>
       </c>
       <c r="S15">
-        <v>3.901062974911073</v>
+        <v>3.312861259538954</v>
       </c>
       <c r="T15">
-        <v>6.798990815620525</v>
+        <v>6.677878086091871</v>
       </c>
       <c r="U15">
-        <v>7.560695799479248</v>
+        <v>8.302001048492793</v>
       </c>
       <c r="V15">
-        <v>97.68269830329515</v>
+        <v>105.1417882013693</v>
       </c>
       <c r="W15">
-        <v>155.4248619133289</v>
+        <v>189.9491216044831</v>
       </c>
       <c r="Z15">
-        <v>-1.244484706044522E-14</v>
+        <v>1.556979026707701E-14</v>
       </c>
       <c r="AA15">
-        <v>9.877747521252022</v>
+        <v>11.1055152471747</v>
       </c>
       <c r="AB15">
-        <v>4.247479121115452</v>
+        <v>5.194462144308943</v>
       </c>
       <c r="AC15">
-        <v>5.395673361253727E-17</v>
+        <v>2.063984345337407E-16</v>
       </c>
       <c r="AD15">
-        <v>1.179171415128862</v>
+        <v>1.03155306216269</v>
       </c>
       <c r="AE15">
-        <v>12.8013163028547</v>
+        <v>0.1647420872935314</v>
       </c>
       <c r="AF15">
-        <v>30.01767548010165</v>
+        <v>27.24694822684423</v>
       </c>
       <c r="AG15">
-        <v>0.9208059677226731</v>
+        <v>0.6947002930978334</v>
       </c>
       <c r="AH15">
-        <v>1168.01018747324</v>
+        <v>1348.027185219588</v>
       </c>
       <c r="AJ15">
-        <v>24.67101241233991</v>
+        <v>29.8412622664133</v>
       </c>
       <c r="AK15">
-        <v>590.7173336762028</v>
+        <v>655.9368057105571</v>
       </c>
       <c r="AL15">
-        <v>163.9835451520473</v>
+        <v>173.8675610250219</v>
       </c>
       <c r="AM15">
-        <v>840.3875774762752</v>
+        <v>1084.721449923174</v>
       </c>
       <c r="AN15">
-        <v>23.62720312533175</v>
+        <v>25.77257946896036</v>
       </c>
       <c r="AO15">
-        <v>51.96974369851915</v>
+        <v>69.57830254773263</v>
       </c>
       <c r="AP15">
-        <v>543.1050233050847</v>
+        <v>625.7126515469354</v>
       </c>
       <c r="AQ15">
-        <v>38.26868570107502</v>
+        <v>37.34626431124438</v>
       </c>
       <c r="AR15">
-        <v>20.61806004100884</v>
+        <v>20.75738817746239</v>
       </c>
       <c r="AS15">
-        <v>2.815000164619893</v>
+        <v>3.864291192817406</v>
       </c>
       <c r="AT15">
-        <v>3.968384019463474</v>
+        <v>5.264389053214085</v>
       </c>
       <c r="AU15">
-        <v>68.39240582123874</v>
+        <v>93.99051634296788</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2450,121 +2435,124 @@
         </is>
       </c>
       <c r="B16">
-        <v>240.6567297230465</v>
+        <v>291.4390704453126</v>
       </c>
       <c r="C16">
-        <v>70.17275611024441</v>
+        <v>80.10491253916459</v>
       </c>
       <c r="D16">
-        <v>6246.753892109907</v>
+        <v>6996.820680797216</v>
       </c>
       <c r="E16">
-        <v>130.0366677033113</v>
+        <v>171.184136872569</v>
       </c>
       <c r="F16">
-        <v>234.3823215586307</v>
+        <v>282.2641288229636</v>
       </c>
       <c r="G16">
-        <v>3.214875130434783</v>
+        <v>4.245579507162223</v>
       </c>
       <c r="H16">
-        <v>36.5117570890018</v>
+        <v>53.79397032866993</v>
       </c>
       <c r="I16">
-        <v>167.8007835335665</v>
+        <v>180.7882249916112</v>
       </c>
       <c r="J16">
-        <v>41.72010401717557</v>
+        <v>42.39975384988481</v>
       </c>
       <c r="K16">
-        <v>8.105139659646593E-15</v>
+        <v>1.627144785433848E-14</v>
       </c>
       <c r="L16">
-        <v>4309.694827718855</v>
+        <v>4938.097759055293</v>
       </c>
       <c r="M16">
-        <v>624.4779149797571</v>
+        <v>606.8969612801482</v>
       </c>
       <c r="N16">
-        <v>1190.943670688431</v>
+        <v>1245.567120769511</v>
       </c>
       <c r="O16">
-        <v>99.79540607563546</v>
+        <v>146.0338744724025</v>
       </c>
       <c r="P16">
-        <v>10.33751080103427</v>
+        <v>3.051979000954502</v>
+      </c>
+      <c r="Q16">
+        <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>11.00555771940337</v>
+        <v>17.87985999411199</v>
       </c>
       <c r="T16">
-        <v>6.296718135284911</v>
+        <v>8.024679851184649</v>
       </c>
       <c r="U16">
-        <v>4.131665274587596</v>
+        <v>5.799686100866053</v>
       </c>
       <c r="V16">
-        <v>71.60947933227345</v>
+        <v>76.63342910560525</v>
       </c>
       <c r="W16">
-        <v>142.4694250598417</v>
+        <v>179.1273568510987</v>
       </c>
       <c r="Z16">
-        <v>-1.30610943256942E-14</v>
+        <v>-2.03558877123509E-14</v>
       </c>
       <c r="AA16">
-        <v>2.372193032552827</v>
+        <v>2.879939694927279</v>
       </c>
       <c r="AB16">
-        <v>1.570459691249228</v>
+        <v>1.995154721626862</v>
       </c>
       <c r="AC16">
-        <v>1.427833521047625E-16</v>
+        <v>9.530354110780047E-17</v>
       </c>
       <c r="AF16">
-        <v>62.44166000584853</v>
+        <v>72.096591650026</v>
       </c>
       <c r="AG16">
-        <v>1.185679434666958</v>
+        <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>2617.144988662131</v>
+        <v>2875.304034390516</v>
       </c>
       <c r="AJ16">
-        <v>54.5265874446812</v>
+        <v>56.73081840255633</v>
       </c>
       <c r="AK16">
-        <v>850.1884882198952</v>
+        <v>950.3996894883813</v>
       </c>
       <c r="AL16">
-        <v>148.9070474516696</v>
+        <v>145.9637409928347</v>
       </c>
       <c r="AM16">
-        <v>382.7332060027285</v>
+        <v>530.4818836437121</v>
       </c>
       <c r="AN16">
-        <v>63.82977970444959</v>
+        <v>56.70973700887199</v>
       </c>
       <c r="AO16">
-        <v>18.78622684805755</v>
+        <v>19.65829846993825</v>
       </c>
       <c r="AP16">
-        <v>518.4741599737748</v>
+        <v>482.3446206170599</v>
       </c>
       <c r="AQ16">
-        <v>26.89619648490311</v>
+        <v>29.57987938026213</v>
       </c>
       <c r="AR16">
-        <v>7.277308379932151</v>
+        <v>7.682049072411729</v>
       </c>
       <c r="AS16">
-        <v>4.333032678999997</v>
+        <v>6.263969477183439</v>
       </c>
       <c r="AT16">
-        <v>1.374850477065183</v>
+        <v>0.5393222515324018</v>
       </c>
       <c r="AU16">
-        <v>28.04398730684338</v>
+        <v>42.31083223451127</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2577,124 +2565,124 @@
         </is>
       </c>
       <c r="B17">
-        <v>229.4724309258362</v>
+        <v>266.1701260393688</v>
       </c>
       <c r="C17">
-        <v>178.9010978642937</v>
+        <v>183.0127926401162</v>
       </c>
       <c r="D17">
-        <v>4748.423195951424</v>
+        <v>5287.858326176391</v>
       </c>
       <c r="E17">
-        <v>128.5714363266027</v>
+        <v>155.1909377051324</v>
       </c>
       <c r="F17">
-        <v>214.5216456859791</v>
+        <v>250.0577371621931</v>
       </c>
       <c r="G17">
-        <v>11.93982584988594</v>
+        <v>15.29497140565417</v>
       </c>
       <c r="H17">
-        <v>10.62995366410499</v>
+        <v>0.9436809027281817</v>
       </c>
       <c r="I17">
-        <v>149.5740518052836</v>
+        <v>150.9753512885255</v>
       </c>
       <c r="J17">
-        <v>42.26915306258483</v>
+        <v>43.64769451014565</v>
       </c>
       <c r="K17">
-        <v>3.824293611475799E-15</v>
+        <v>-4.321923144748099E-15</v>
       </c>
       <c r="L17">
-        <v>3165.040522046786</v>
+        <v>3495.409540745444</v>
       </c>
       <c r="M17">
-        <v>656.8325289600732</v>
+        <v>713.5210797713682</v>
       </c>
       <c r="N17">
-        <v>954.0534940416537</v>
+        <v>970.0441239555864</v>
       </c>
       <c r="O17">
-        <v>59.89156772483385</v>
+        <v>96.742461784969</v>
       </c>
       <c r="P17">
-        <v>7.529179376718966</v>
+        <v>3.390967873712468</v>
       </c>
       <c r="S17">
-        <v>37.82362546346901</v>
+        <v>29.38158241760009</v>
       </c>
       <c r="T17">
-        <v>8.977446754969918</v>
+        <v>10.73981639816398</v>
       </c>
       <c r="U17">
-        <v>5.067695937966597</v>
+        <v>5.926866645478509</v>
       </c>
       <c r="V17">
-        <v>74.06373192972052</v>
+        <v>84.25669615552911</v>
       </c>
       <c r="W17">
-        <v>110.0223047840974</v>
+        <v>130.9728340457765</v>
       </c>
       <c r="Z17">
-        <v>-9.863615490526144E-15</v>
+        <v>1.35876188995868E-14</v>
       </c>
       <c r="AA17">
-        <v>5.80895074537214</v>
+        <v>7.166877748603852</v>
       </c>
       <c r="AB17">
-        <v>5.123578804490949</v>
+        <v>6.65138338110388</v>
       </c>
       <c r="AC17">
-        <v>1.794340134232904E-16</v>
+        <v>5.264254386072237E-17</v>
       </c>
       <c r="AE17">
-        <v>0.9010921793683611</v>
+        <v>0.9436809027281817</v>
       </c>
       <c r="AF17">
-        <v>24.74892429279307</v>
+        <v>13.54241604247699</v>
       </c>
       <c r="AG17">
-        <v>10.19173718603804</v>
+        <v>0.1841582581446207</v>
       </c>
       <c r="AH17">
-        <v>1829.569947190461</v>
+        <v>2042.188966069165</v>
       </c>
       <c r="AJ17">
-        <v>35.8038669374595</v>
+        <v>38.14387974006627</v>
       </c>
       <c r="AK17">
-        <v>615.9283767188508</v>
+        <v>715.8754019440919</v>
       </c>
       <c r="AL17">
-        <v>120.4159292890429</v>
+        <v>120.5601686851196</v>
       </c>
       <c r="AM17">
-        <v>307.1593131313132</v>
+        <v>415.1102100266659</v>
       </c>
       <c r="AN17">
-        <v>29.85728894420244</v>
+        <v>31.33296586787364</v>
       </c>
       <c r="AO17">
-        <v>28.78200698160438</v>
+        <v>10.07119967348413</v>
       </c>
       <c r="AP17">
-        <v>516.0193953224002</v>
+        <v>558.0586070106664</v>
       </c>
       <c r="AQ17">
-        <v>46.67626494768938</v>
+        <v>57.44121163158965</v>
       </c>
       <c r="AR17">
-        <v>4.944099173895731</v>
+        <v>9.561047297297298</v>
       </c>
       <c r="AS17">
-        <v>11.08494747460339</v>
+        <v>16.61842488703986</v>
       </c>
       <c r="AT17">
-        <v>0.6724074347273797</v>
+        <v>1.70778661939267</v>
       </c>
       <c r="AU17">
-        <v>59.45119471525416</v>
+        <v>67.34798832464037</v>
       </c>
       <c r="AV17">
         <v>1</v>
@@ -2707,121 +2695,124 @@
         </is>
       </c>
       <c r="B18">
-        <v>296.6708614976806</v>
+        <v>321.558614616558</v>
       </c>
       <c r="C18">
-        <v>66.12332738653201</v>
+        <v>76.79050534878537</v>
       </c>
       <c r="D18">
-        <v>6543.778237644254</v>
+        <v>7344.553798245614</v>
       </c>
       <c r="E18">
-        <v>135.5227392872254</v>
+        <v>162.7166963482641</v>
       </c>
       <c r="F18">
-        <v>286.7828499891139</v>
+        <v>308.0231876758999</v>
       </c>
       <c r="G18">
-        <v>2.883318036419235</v>
+        <v>3.076966858789625</v>
       </c>
       <c r="H18">
-        <v>2.298640061396777</v>
+        <v>1.465901960784314</v>
       </c>
       <c r="I18">
-        <v>172.768738200732</v>
+        <v>192.1125416289201</v>
       </c>
       <c r="J18">
-        <v>52.08348273832875</v>
+        <v>62.13437882607131</v>
       </c>
       <c r="K18">
-        <v>-2.362363152320533E-15</v>
+        <v>1.002715950275063E-14</v>
       </c>
       <c r="L18">
-        <v>4548.067781450343</v>
+        <v>5410.822688450339</v>
       </c>
       <c r="M18">
-        <v>584.7006963192219</v>
+        <v>612.6089078947368</v>
       </c>
       <c r="N18">
-        <v>1107.022606975909</v>
+        <v>1192.041047060297</v>
       </c>
       <c r="O18">
-        <v>118.2904431385909</v>
+        <v>132.4650766580534</v>
       </c>
       <c r="P18">
-        <v>7.668817730426269</v>
+        <v>5.05320796460177</v>
       </c>
       <c r="S18">
-        <v>3.838836099097505</v>
+        <v>8.179900921429818</v>
       </c>
       <c r="T18">
-        <v>2.483350629312055</v>
+        <v>2.886544113257357</v>
       </c>
       <c r="U18">
-        <v>2.571382935153584</v>
+        <v>2.444430619421152</v>
       </c>
       <c r="V18">
-        <v>95.7637440878808</v>
+        <v>110.699778597786</v>
       </c>
       <c r="W18">
-        <v>157.8718591279348</v>
+        <v>182.9373819823209</v>
       </c>
       <c r="Z18">
-        <v>1.20065307164743E-14</v>
+        <v>-1.130913888405465E-14</v>
       </c>
       <c r="AA18">
-        <v>1.613260369755571</v>
+        <v>1.192546403712297</v>
       </c>
       <c r="AB18">
-        <v>1.000605794003377</v>
+        <v>1.582942839963171</v>
       </c>
       <c r="AC18">
-        <v>4.385066428632416E-17</v>
+        <v>3.395429935321545E-17</v>
+      </c>
+      <c r="AE18">
+        <v>1.465901960784314</v>
       </c>
       <c r="AF18">
-        <v>22.44730437178587</v>
+        <v>53.42008340109989</v>
       </c>
       <c r="AG18">
-        <v>0.5691056910569106</v>
+        <v>0.2359013659281808</v>
       </c>
       <c r="AH18">
-        <v>2480.186461287693</v>
+        <v>2753.727165225901</v>
       </c>
       <c r="AJ18">
-        <v>47.4107379882475</v>
+        <v>48.79836248694467</v>
       </c>
       <c r="AK18">
-        <v>804.2363556969087</v>
+        <v>1034.992305270732</v>
       </c>
       <c r="AL18">
-        <v>170.4406188166369</v>
+        <v>167.6571106442577</v>
       </c>
       <c r="AM18">
-        <v>791.7395334909377</v>
+        <v>1030.696044189505</v>
       </c>
       <c r="AN18">
-        <v>85.63331242740998</v>
+        <v>88.5120352708787</v>
       </c>
       <c r="AO18">
-        <v>43.82748070894614</v>
+        <v>28.34323659306002</v>
       </c>
       <c r="AP18">
-        <v>468.0822964626614</v>
+        <v>523.5928768750928</v>
       </c>
       <c r="AQ18">
-        <v>23.43052514792899</v>
+        <v>25.77509433962264</v>
       </c>
       <c r="AR18">
-        <v>43.50620699881376</v>
+        <v>11.28688509874327</v>
       </c>
       <c r="AS18">
-        <v>3.961703532518983</v>
+        <v>5.29785731104309</v>
       </c>
       <c r="AT18">
-        <v>0.2184070995281959</v>
+        <v>0.1449608633696535</v>
       </c>
       <c r="AU18">
-        <v>42.65683665649364</v>
+        <v>28.35798620094873</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2834,130 +2825,130 @@
         </is>
       </c>
       <c r="B19">
-        <v>722.3841717975672</v>
+        <v>831.1411416349174</v>
       </c>
       <c r="C19">
-        <v>147.2531469362556</v>
+        <v>152.9423312368973</v>
       </c>
       <c r="D19">
-        <v>6141.010663941129</v>
+        <v>6739.003798312177</v>
       </c>
       <c r="E19">
-        <v>382.5710962508213</v>
+        <v>579.8809178338358</v>
       </c>
       <c r="F19">
-        <v>643.9961210343909</v>
+        <v>748.2371907687199</v>
       </c>
       <c r="G19">
-        <v>68.18604724456924</v>
+        <v>78.4037210372871</v>
       </c>
       <c r="H19">
-        <v>1.167434799309154</v>
+        <v>1.114156500116559</v>
       </c>
       <c r="I19">
-        <v>264.2445316570177</v>
+        <v>290.7155719199224</v>
       </c>
       <c r="J19">
-        <v>89.41902221804276</v>
+        <v>92.58359732217734</v>
       </c>
       <c r="K19">
-        <v>1.030714691227961E-14</v>
+        <v>9.01885046691469E-15</v>
       </c>
       <c r="L19">
-        <v>3222.969769654482</v>
+        <v>3530.148246852933</v>
       </c>
       <c r="M19">
-        <v>1883.39394278607</v>
+        <v>2047.749087503746</v>
       </c>
       <c r="N19">
-        <v>846.0090025878803</v>
+        <v>880.6605726330586</v>
       </c>
       <c r="O19">
-        <v>246.2275321336761</v>
+        <v>380.7239411893422</v>
       </c>
       <c r="P19">
-        <v>14.25588715906402</v>
+        <v>14.8962916975102</v>
       </c>
       <c r="Q19">
-        <v>0.7059992909711335</v>
+        <v>0.7121344119477288</v>
       </c>
       <c r="R19">
-        <v>1.008327763829577</v>
+        <v>0.4830715219652364</v>
       </c>
       <c r="S19">
-        <v>58.6441595337815</v>
+        <v>57.43528956865308</v>
       </c>
       <c r="T19">
-        <v>107.4086381268073</v>
+        <v>122.0721735045412</v>
       </c>
       <c r="U19">
-        <v>90.32612573218462</v>
+        <v>104.0514904924074</v>
       </c>
       <c r="V19">
-        <v>174.1517608382437</v>
+        <v>199.6363684020246</v>
       </c>
       <c r="W19">
-        <v>214.7967634854772</v>
+        <v>267.6942153144239</v>
       </c>
       <c r="Z19">
-        <v>3.20218186843446E-14</v>
+        <v>3.771452881734343E-14</v>
       </c>
       <c r="AA19">
-        <v>19.44677173333333</v>
+        <v>20.97509145475578</v>
       </c>
       <c r="AB19">
-        <v>47.07910305177857</v>
+        <v>55.96742761701785</v>
       </c>
       <c r="AC19">
-        <v>9.516062335733174E-16</v>
+        <v>-6.519675281526367E-16</v>
       </c>
       <c r="AD19">
-        <v>0.9010232515984443</v>
+        <v>1.058232020667504</v>
       </c>
       <c r="AF19">
-        <v>2.785638105818637</v>
+        <v>0.6118350421243341</v>
       </c>
       <c r="AG19">
-        <v>1.097157080586214</v>
+        <v>0.3103345454545466</v>
       </c>
       <c r="AH19">
-        <v>2375.357483631871</v>
+        <v>2632.805727536407</v>
       </c>
       <c r="AJ19">
-        <v>52.00706158441189</v>
+        <v>55.45168360744879</v>
       </c>
       <c r="AK19">
-        <v>370.5158020627606</v>
+        <v>405.4835174941225</v>
       </c>
       <c r="AL19">
-        <v>87.88577772122909</v>
+        <v>86.90551884667367</v>
       </c>
       <c r="AM19">
-        <v>19.43765595463138</v>
+        <v>41.32278752436648</v>
       </c>
       <c r="AN19">
-        <v>23.44991979355559</v>
+        <v>25.24876890551309</v>
       </c>
       <c r="AO19">
-        <v>140.8388710378667</v>
+        <v>131.9517217753949</v>
       </c>
       <c r="AP19">
-        <v>1498.307835328905</v>
+        <v>1558.851002938667</v>
       </c>
       <c r="AQ19">
-        <v>206.623787835111</v>
+        <v>220.1558575279708</v>
       </c>
       <c r="AR19">
-        <v>58.38168938666759</v>
+        <v>62.70764761961508</v>
       </c>
       <c r="AS19">
-        <v>13.84810292354515</v>
+        <v>44.008586333302</v>
       </c>
       <c r="AT19">
-        <v>1.280722527085971</v>
+        <v>1.421895635673624</v>
       </c>
       <c r="AU19">
-        <v>79.38300684485017</v>
+        <v>120.0037066814528</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2970,127 +2961,127 @@
         </is>
       </c>
       <c r="B20">
-        <v>823.5143643585774</v>
+        <v>847.272864469354</v>
       </c>
       <c r="C20">
-        <v>264.944776008122</v>
+        <v>303.0227739143774</v>
       </c>
       <c r="D20">
-        <v>6604.081642127781</v>
+        <v>7498.808673732616</v>
       </c>
       <c r="E20">
-        <v>366.2824524546661</v>
+        <v>378.530268288201</v>
       </c>
       <c r="F20">
-        <v>758.3182291666667</v>
+        <v>795.1421101700079</v>
       </c>
       <c r="G20">
-        <v>61.920152168626</v>
+        <v>74.30895041198855</v>
       </c>
       <c r="H20">
-        <v>24.42975831489418</v>
+        <v>9.326571642910727</v>
       </c>
       <c r="I20">
-        <v>216.1149734946989</v>
+        <v>252.8451762110522</v>
       </c>
       <c r="J20">
-        <v>65.38599200944338</v>
+        <v>81.26611483277996</v>
       </c>
       <c r="K20">
-        <v>-7.051787888266577E-15</v>
+        <v>1.025239653031422E-14</v>
       </c>
       <c r="L20">
-        <v>3596.839036621463</v>
+        <v>4143.905765941486</v>
       </c>
       <c r="M20">
-        <v>1748.196575864762</v>
+        <v>1838.153463436518</v>
       </c>
       <c r="N20">
-        <v>809.7157671967117</v>
+        <v>902.7588777680462</v>
       </c>
       <c r="O20">
-        <v>224.5318576838748</v>
+        <v>252.4300090094362</v>
       </c>
       <c r="P20">
-        <v>14.84097307620983</v>
+        <v>9.093369310152365</v>
       </c>
       <c r="Q20">
-        <v>0.5855579468417088</v>
+        <v>1.869257194710915</v>
       </c>
       <c r="R20">
-        <v>0.2530447830817162</v>
+        <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>67.30643870576338</v>
+        <v>84.73842292239345</v>
       </c>
       <c r="T20">
-        <v>152.4469663624168</v>
+        <v>176.7574058280028</v>
       </c>
       <c r="U20">
-        <v>27.35302931758847</v>
+        <v>34.26633079900855</v>
       </c>
       <c r="V20">
-        <v>300.6534890891841</v>
+        <v>300.8105811423964</v>
       </c>
       <c r="W20">
-        <v>245.0563589089169</v>
+        <v>284.1735439362736</v>
       </c>
       <c r="Z20">
-        <v>5.087705243009618E-14</v>
+        <v>2.497931604560911E-14</v>
       </c>
       <c r="AA20">
-        <v>23.20802520709283</v>
+        <v>24.45198143187045</v>
       </c>
       <c r="AB20">
-        <v>40.56166833778965</v>
+        <v>46.46207692312383</v>
       </c>
       <c r="AC20">
-        <v>1.366120468303309E-15</v>
+        <v>3.647694634457333E-16</v>
       </c>
       <c r="AF20">
-        <v>65.42282526706236</v>
+        <v>20.27729746292588</v>
       </c>
       <c r="AG20">
-        <v>6.700529722408637</v>
+        <v>9.326571642910727</v>
       </c>
       <c r="AH20">
-        <v>1130.531897083114</v>
+        <v>1255.659712219742</v>
       </c>
       <c r="AJ20">
-        <v>1307.550031665175</v>
+        <v>1398.226863494702</v>
       </c>
       <c r="AK20">
-        <v>654.0236009922367</v>
+        <v>725.489685459114</v>
       </c>
       <c r="AL20">
-        <v>97.49151532847392</v>
+        <v>93.31445792487625</v>
       </c>
       <c r="AM20">
-        <v>69.82745615849049</v>
+        <v>28.41458214553638</v>
       </c>
       <c r="AN20">
-        <v>14.35233252220736</v>
+        <v>15.44954236439457</v>
       </c>
       <c r="AO20">
-        <v>26.66866820706954</v>
+        <v>23.94215407575887</v>
       </c>
       <c r="AP20">
-        <v>1158.502890505554</v>
+        <v>1299.434950578142</v>
       </c>
       <c r="AQ20">
-        <v>117.8553116516151</v>
+        <v>123.4993852424784</v>
       </c>
       <c r="AR20">
-        <v>64.76130682582178</v>
+        <v>69.17810064424573</v>
       </c>
       <c r="AS20">
-        <v>7.309776106189224</v>
+        <v>12.6261611504851</v>
       </c>
       <c r="AT20">
-        <v>166.8280098759952</v>
+        <v>168.5801743586084</v>
       </c>
       <c r="AU20">
-        <v>90.97214384147675</v>
+        <v>81.69165895556567</v>
       </c>
       <c r="AV20">
         <v>1</v>
@@ -3103,121 +3094,124 @@
         </is>
       </c>
       <c r="B21">
-        <v>315.2268413951376</v>
+        <v>358.8138940597283</v>
       </c>
       <c r="C21">
-        <v>51.22387830970848</v>
+        <v>54.52463813522512</v>
       </c>
       <c r="D21">
-        <v>6079.333988121729</v>
+        <v>6646.014956370884</v>
       </c>
       <c r="E21">
-        <v>110.7099994978057</v>
+        <v>163.2076701351378</v>
       </c>
       <c r="F21">
-        <v>306.3596955787229</v>
+        <v>341.9858903409284</v>
       </c>
       <c r="G21">
-        <v>8.97868773502698</v>
+        <v>10.13563396349413</v>
       </c>
       <c r="H21">
-        <v>3.351476764317604</v>
+        <v>0.521964</v>
       </c>
       <c r="I21">
-        <v>199.9692401984629</v>
+        <v>236.4102375485325</v>
       </c>
       <c r="J21">
-        <v>40.44908390469771</v>
+        <v>43.33131144990888</v>
       </c>
       <c r="K21">
-        <v>7.689813873951203E-15</v>
+        <v>4.232314952314986E-15</v>
       </c>
       <c r="L21">
-        <v>4134.978309464279</v>
+        <v>4435.711389076641</v>
       </c>
       <c r="M21">
-        <v>677.3344198464326</v>
+        <v>748.530728803414</v>
       </c>
       <c r="N21">
-        <v>1099.893420993031</v>
+        <v>1248.715765316147</v>
       </c>
       <c r="O21">
-        <v>71.97978217047728</v>
+        <v>99.90488891468262</v>
       </c>
       <c r="P21">
-        <v>26.15235013623978</v>
+        <v>12.89748274030802</v>
       </c>
       <c r="S21">
-        <v>16.4747989931617</v>
+        <v>18.72185083755225</v>
       </c>
       <c r="T21">
-        <v>9.413426059347568</v>
+        <v>12.34749365930467</v>
       </c>
       <c r="U21">
-        <v>5.050277153132802</v>
+        <v>5.526191383943639</v>
       </c>
       <c r="V21">
-        <v>119.0373493975904</v>
+        <v>117.2128451934936</v>
       </c>
       <c r="W21">
-        <v>150.0551755323546</v>
+        <v>178.4133746360911</v>
       </c>
       <c r="Z21">
-        <v>1.063209241906351E-14</v>
+        <v>9.412490184663567E-15</v>
       </c>
       <c r="AA21">
-        <v>5.50843112775697</v>
+        <v>6.589703349282297</v>
       </c>
       <c r="AB21">
-        <v>3.831361626135043</v>
+        <v>3.921611554541999</v>
       </c>
       <c r="AC21">
-        <v>3.603671851069531E-17</v>
+        <v>-8.640041794698817E-17</v>
+      </c>
+      <c r="AE21">
+        <v>0.1388024948024948</v>
       </c>
       <c r="AF21">
-        <v>40.08701063298366</v>
+        <v>50.30145842180319</v>
       </c>
       <c r="AG21">
-        <v>0.295232794893354</v>
+        <v>0.3286176631925398</v>
       </c>
       <c r="AH21">
-        <v>2398.656005044108</v>
+        <v>2664.704169931044</v>
       </c>
       <c r="AJ21">
-        <v>67.96043170021521</v>
+        <v>68.6075730323935</v>
       </c>
       <c r="AK21">
-        <v>756.2954631442776</v>
+        <v>817.7484417498706</v>
       </c>
       <c r="AL21">
-        <v>128.2675041049768</v>
+        <v>125.7989090856873</v>
       </c>
       <c r="AM21">
-        <v>160.1202959247445</v>
+        <v>202.9597743589744</v>
       </c>
       <c r="AN21">
-        <v>47.54875280202272</v>
+        <v>44.12978860820852</v>
       </c>
       <c r="AO21">
-        <v>26.66968210456692</v>
+        <v>28.92845380960833</v>
       </c>
       <c r="AP21">
-        <v>546.7773933726539</v>
+        <v>615.6282835942753</v>
       </c>
       <c r="AQ21">
-        <v>36.61654898566105</v>
+        <v>35.29846140465258</v>
       </c>
       <c r="AR21">
-        <v>19.79675333245348</v>
+        <v>28.39506172839506</v>
       </c>
       <c r="AS21">
-        <v>1.87222457071148</v>
+        <v>2.801635389304237</v>
       </c>
       <c r="AT21">
-        <v>11.89844339160372</v>
+        <v>8.014175358539767</v>
       </c>
       <c r="AU21">
-        <v>34.28656392364979</v>
+        <v>41.6753035873318</v>
       </c>
       <c r="AV21">
         <v>1</v>
@@ -3230,124 +3224,127 @@
         </is>
       </c>
       <c r="B22">
-        <v>593.4518074934674</v>
+        <v>638.6891898093417</v>
       </c>
       <c r="C22">
-        <v>188.5875488951804</v>
+        <v>150.9686019679605</v>
       </c>
       <c r="D22">
-        <v>5856.357215341963</v>
+        <v>6486.945039533327</v>
       </c>
       <c r="E22">
-        <v>412.6389472863771</v>
+        <v>619.9970199744042</v>
       </c>
       <c r="F22">
-        <v>516.8807782335937</v>
+        <v>556.9778057321757</v>
       </c>
       <c r="G22">
-        <v>75.61454123838504</v>
+        <v>79.21314675951569</v>
       </c>
       <c r="H22">
-        <v>12.48128356724007</v>
+        <v>7.393030927835052</v>
       </c>
       <c r="I22">
-        <v>186.0801891307704</v>
+        <v>203.677351311801</v>
       </c>
       <c r="J22">
-        <v>47.02178090579927</v>
+        <v>47.57662715714164</v>
       </c>
       <c r="K22">
-        <v>1.20385017788511E-14</v>
+        <v>2.452554866325957E-15</v>
       </c>
       <c r="L22">
-        <v>2555.19149116263</v>
+        <v>2884.141888816832</v>
       </c>
       <c r="M22">
-        <v>2153.068990731436</v>
+        <v>2374.060967217833</v>
       </c>
       <c r="N22">
-        <v>980.3972933387452</v>
+        <v>1117.82554002121</v>
       </c>
       <c r="O22">
-        <v>329.0247788671329</v>
+        <v>554.7411823598095</v>
       </c>
       <c r="P22">
-        <v>14.82878063067461</v>
+        <v>13.40371279393796</v>
       </c>
       <c r="Q22">
-        <v>0.02751221529950105</v>
+        <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>44.0796664136743</v>
+        <v>46.07677786843765</v>
       </c>
       <c r="T22">
-        <v>65.38933080137329</v>
+        <v>71.48853168715587</v>
       </c>
       <c r="U22">
-        <v>48.12487340179419</v>
+        <v>57.40595109536271</v>
       </c>
       <c r="V22">
-        <v>143.4172425389066</v>
+        <v>160.1128887958049</v>
       </c>
       <c r="W22">
-        <v>199.3113674412031</v>
+        <v>234.0157372262774</v>
       </c>
       <c r="Z22">
-        <v>-1.740015968058004E-14</v>
+        <v>-2.659003360762531E-14</v>
       </c>
       <c r="AA22">
-        <v>16.21553534022619</v>
+        <v>17.36832762194483</v>
       </c>
       <c r="AB22">
-        <v>53.84211623103562</v>
+        <v>64.104336935167</v>
       </c>
       <c r="AC22">
-        <v>-5.116257441633771E-15</v>
+        <v>-2.121270441452894E-15</v>
       </c>
       <c r="AD22">
-        <v>2.462730908152735</v>
+        <v>2.404985727444346</v>
       </c>
       <c r="AF22">
-        <v>19.53195629128272</v>
+        <v>17.8540614529705</v>
+      </c>
+      <c r="AG22">
+        <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>1626.185746554911</v>
+        <v>1816.00229332501</v>
       </c>
       <c r="AJ22">
-        <v>36.15014201508941</v>
+        <v>40.51471405928525</v>
       </c>
       <c r="AK22">
-        <v>575.3927118851334</v>
+        <v>721.25747719356</v>
       </c>
       <c r="AL22">
-        <v>87.50244663049796</v>
+        <v>92.83584864012353</v>
       </c>
       <c r="AM22">
-        <v>16.45390103567319</v>
+        <v>26.82640379784006</v>
       </c>
       <c r="AN22">
-        <v>22.11524453823237</v>
+        <v>23.85031912715728</v>
       </c>
       <c r="AO22">
-        <v>71.59530494845382</v>
+        <v>76.31042567803429</v>
       </c>
       <c r="AP22">
-        <v>1511.208308682148</v>
+        <v>1742.589515567835</v>
       </c>
       <c r="AQ22">
-        <v>149.5809419829885</v>
+        <v>150.5866521995416</v>
       </c>
       <c r="AR22">
-        <v>29.8673729980497</v>
+        <v>54.11215648027741</v>
       </c>
       <c r="AS22">
-        <v>11.71783918478504</v>
+        <v>12.87079444658696</v>
       </c>
       <c r="AT22">
-        <v>4.594612289655365</v>
+        <v>7.371706646819717</v>
       </c>
       <c r="AU22">
-        <v>277.2977506183117</v>
+        <v>335.1322091530582</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3360,115 +3357,115 @@
         </is>
       </c>
       <c r="B23">
-        <v>352.1733504832935</v>
+        <v>405.9330603392818</v>
       </c>
       <c r="C23">
-        <v>24.79586408964737</v>
+        <v>33.43016992961698</v>
       </c>
       <c r="D23">
-        <v>4871.0665517626</v>
+        <v>5328.321989900858</v>
       </c>
       <c r="E23">
-        <v>133.4857216659634</v>
+        <v>161.2899871266379</v>
       </c>
       <c r="F23">
-        <v>322.8931265490691</v>
+        <v>378.9341546061154</v>
       </c>
       <c r="G23">
-        <v>8.751418706854292</v>
+        <v>8.314697869237811</v>
       </c>
       <c r="H23">
-        <v>35.2748049806933</v>
+        <v>37.97439035998615</v>
       </c>
       <c r="I23">
-        <v>121.07005478881</v>
+        <v>130.7338973216033</v>
       </c>
       <c r="J23">
-        <v>24.79586408964737</v>
+        <v>33.43016992961698</v>
       </c>
       <c r="K23">
-        <v>-1.584660110922632E-14</v>
+        <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>1854.341032250798</v>
+        <v>2455.749916885717</v>
       </c>
       <c r="M23">
-        <v>1329.878874192325</v>
+        <v>1171.809780823175</v>
       </c>
       <c r="N23">
-        <v>1464.314431301145</v>
+        <v>1654.247831668484</v>
       </c>
       <c r="O23">
-        <v>103.9253714846022</v>
+        <v>145.4503925535566</v>
       </c>
       <c r="P23">
-        <v>3.734349412322025</v>
+        <v>4.84756237679643</v>
       </c>
       <c r="S23">
-        <v>6.119925241477684</v>
+        <v>11.70025905942798</v>
       </c>
       <c r="T23">
-        <v>12.09506806082709</v>
+        <v>14.93405394990366</v>
       </c>
       <c r="U23">
-        <v>12.89785946620327</v>
+        <v>19.02889005259758</v>
       </c>
       <c r="V23">
-        <v>246.5758282253477</v>
+        <v>240.4124573779354</v>
       </c>
       <c r="W23">
-        <v>89.58243467401425</v>
+        <v>114.790159407184</v>
       </c>
       <c r="Z23">
-        <v>1.478853173614518E-14</v>
+        <v>2.558578501690875E-15</v>
       </c>
       <c r="AA23">
-        <v>5.563021083857273</v>
+        <v>5.455019706168157</v>
       </c>
       <c r="AB23">
-        <v>4.488002623959464</v>
+        <v>3.872188906195916</v>
       </c>
       <c r="AC23">
-        <v>4.351708602381446E-16</v>
+        <v>-6.89598864011319E-16</v>
       </c>
       <c r="AF23">
-        <v>35.2748049806933</v>
+        <v>37.97439035998615</v>
       </c>
       <c r="AH23">
-        <v>706.2103903173514</v>
+        <v>747.2993643579418</v>
       </c>
       <c r="AJ23">
-        <v>12.77891651615127</v>
+        <v>13.19621665544673</v>
       </c>
       <c r="AK23">
-        <v>640.7268557395059</v>
+        <v>901.4335826701729</v>
       </c>
       <c r="AL23">
-        <v>114.0268134050245</v>
+        <v>125.6519104027669</v>
       </c>
       <c r="AM23">
-        <v>33.7282353568956</v>
+        <v>53.30954009433962</v>
       </c>
       <c r="AN23">
-        <v>26.68615468977789</v>
+        <v>33.52521031496038</v>
       </c>
       <c r="AO23">
-        <v>148.1342405824892</v>
+        <v>198.2237839552116</v>
       </c>
       <c r="AP23">
-        <v>833.8604860619201</v>
+        <v>805.4523550712095</v>
       </c>
       <c r="AQ23">
-        <v>14.15445651655892</v>
+        <v>15.04027135070786</v>
       </c>
       <c r="AR23">
-        <v>13.85449500407323</v>
+        <v>13.19459932804416</v>
       </c>
       <c r="AS23">
-        <v>17.64521051338247</v>
+        <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>397.9241734225781</v>
+        <v>213.4158076003532</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3481,133 +3478,133 @@
         </is>
       </c>
       <c r="B24">
-        <v>791.7109888986269</v>
+        <v>890.2795900229357</v>
       </c>
       <c r="C24">
-        <v>234.6136719364762</v>
+        <v>249.9109374925584</v>
       </c>
       <c r="D24">
-        <v>7296.571729281768</v>
+        <v>7853.07884850879</v>
       </c>
       <c r="E24">
-        <v>681.3059386667695</v>
+        <v>934.4858766834749</v>
       </c>
       <c r="F24">
-        <v>711.98827093316</v>
+        <v>806.5173493975905</v>
       </c>
       <c r="G24">
-        <v>64.1748994740303</v>
+        <v>76.50437958209022</v>
       </c>
       <c r="H24">
-        <v>3.720688242523556</v>
+        <v>5.048908948194662</v>
       </c>
       <c r="I24">
-        <v>219.8372801208285</v>
+        <v>242.5234915183682</v>
       </c>
       <c r="J24">
-        <v>43.43534141865695</v>
+        <v>48.83458032252312</v>
       </c>
       <c r="K24">
-        <v>8.695010499631019E-15</v>
+        <v>5.993375299986348E-15</v>
       </c>
       <c r="L24">
-        <v>3830.543317541272</v>
+        <v>4231.108964536635</v>
       </c>
       <c r="M24">
-        <v>2372.90020779593</v>
+        <v>2453.696065002902</v>
       </c>
       <c r="N24">
-        <v>951.4028527841347</v>
+        <v>1049.334409769335</v>
       </c>
       <c r="O24">
-        <v>462.9548798743301</v>
+        <v>713.2220058543726</v>
       </c>
       <c r="P24">
-        <v>32.43072969374168</v>
+        <v>38.45028534519531</v>
       </c>
       <c r="Q24">
-        <v>0.9380738776727622</v>
+        <v>1.758999341672153</v>
       </c>
       <c r="R24">
-        <v>4.212141359774181</v>
+        <v>1.121639385784391</v>
       </c>
       <c r="S24">
-        <v>88.74963721724374</v>
+        <v>67.56942252344214</v>
       </c>
       <c r="T24">
-        <v>139.1641832785145</v>
+        <v>155.8050776557954</v>
       </c>
       <c r="U24">
-        <v>77.67419514203375</v>
+        <v>89.21995019768856</v>
       </c>
       <c r="V24">
-        <v>189.3211762558902</v>
+        <v>211.3168177063019</v>
       </c>
       <c r="W24">
-        <v>228.0847162196621</v>
+        <v>267.2991257946267</v>
       </c>
       <c r="Z24">
-        <v>2.744780531934216E-14</v>
+        <v>3.265964983221625E-14</v>
       </c>
       <c r="AA24">
-        <v>20.48867416292651</v>
+        <v>21.89121191629795</v>
       </c>
       <c r="AB24">
-        <v>41.28132975117477</v>
+        <v>49.82049445005045</v>
       </c>
       <c r="AC24">
-        <v>-3.420181640241156E-16</v>
+        <v>1.016952704181433E-15</v>
       </c>
       <c r="AD24">
-        <v>3.075609018496673</v>
+        <v>5.048908948194662</v>
       </c>
       <c r="AE24">
-        <v>0.2505468283953072</v>
+        <v>0.2333747907199235</v>
       </c>
       <c r="AF24">
-        <v>20.57280813559476</v>
+        <v>18.98082378032525</v>
       </c>
       <c r="AG24">
-        <v>0.1920380154382731</v>
+        <v>0.255847569760894</v>
       </c>
       <c r="AH24">
-        <v>3085.469750505603</v>
+        <v>3432.443285974499</v>
       </c>
       <c r="AJ24">
-        <v>65.69390122924304</v>
+        <v>69.09989329640791</v>
       </c>
       <c r="AK24">
-        <v>424.2338347160491</v>
+        <v>458.5120723172628</v>
       </c>
       <c r="AL24">
-        <v>93.09099847172695</v>
+        <v>87.39363905325443</v>
       </c>
       <c r="AM24">
-        <v>15.32564942874323</v>
+        <v>25.27516974169742</v>
       </c>
       <c r="AN24">
-        <v>28.52212936610608</v>
+        <v>32.36308133430938</v>
       </c>
       <c r="AO24">
-        <v>101.1848755873087</v>
+        <v>51.04342032892968</v>
       </c>
       <c r="AP24">
-        <v>1772.080896542886</v>
+        <v>1831.83290798451</v>
       </c>
       <c r="AQ24">
-        <v>227.8024643418429</v>
+        <v>228.5320419753087</v>
       </c>
       <c r="AR24">
-        <v>101.8580748899066</v>
+        <v>134.6961730060536</v>
       </c>
       <c r="AS24">
-        <v>5.574692910219325</v>
+        <v>8.790017996400719</v>
       </c>
       <c r="AT24">
-        <v>2.905114920809847</v>
+        <v>2.607946802567986</v>
       </c>
       <c r="AU24">
-        <v>185.6713238886172</v>
+        <v>187.2110484848486</v>
       </c>
       <c r="AV24">
         <v>1</v>
@@ -3620,133 +3617,133 @@
         </is>
       </c>
       <c r="B25">
-        <v>875.1420745160372</v>
+        <v>961.8720139066908</v>
       </c>
       <c r="C25">
-        <v>84.18143315782714</v>
+        <v>92.04650757575757</v>
       </c>
       <c r="D25">
-        <v>6245.96571075934</v>
+        <v>6742.376989425107</v>
       </c>
       <c r="E25">
-        <v>385.9617756065118</v>
+        <v>492.388457869577</v>
       </c>
       <c r="F25">
-        <v>747.6322196261513</v>
+        <v>827.4780925154007</v>
       </c>
       <c r="G25">
-        <v>108.8702994207222</v>
+        <v>118.32339270904</v>
       </c>
       <c r="H25">
-        <v>1.721004315665837</v>
+        <v>1.369760514840421</v>
       </c>
       <c r="I25">
-        <v>208.1845730234411</v>
+        <v>230.4928383356719</v>
       </c>
       <c r="J25">
-        <v>76.03593566024304</v>
+        <v>82.37331214028336</v>
       </c>
       <c r="K25">
-        <v>1.356573197292769E-14</v>
+        <v>-1.235700942162778E-14</v>
       </c>
       <c r="L25">
-        <v>2658.386970475991</v>
+        <v>2917.626195382961</v>
       </c>
       <c r="M25">
-        <v>2547.707543956486</v>
+        <v>2755.595962926831</v>
       </c>
       <c r="N25">
-        <v>996.2092404098692</v>
+        <v>1084.586202808403</v>
       </c>
       <c r="O25">
-        <v>203.2022691113506</v>
+        <v>304.9162703024443</v>
       </c>
       <c r="P25">
-        <v>26.43325373134329</v>
+        <v>32.27975798869263</v>
       </c>
       <c r="Q25">
-        <v>2.350037609270177</v>
+        <v>1.933270295595877</v>
       </c>
       <c r="R25">
-        <v>16.67877592885216</v>
+        <v>10.95951879395962</v>
       </c>
       <c r="S25">
-        <v>56.82360406692875</v>
+        <v>50.13765196676725</v>
       </c>
       <c r="T25">
-        <v>115.420953453866</v>
+        <v>133.1111790741765</v>
       </c>
       <c r="U25">
-        <v>84.74533738938054</v>
+        <v>93.92930347586636</v>
       </c>
       <c r="V25">
-        <v>264.3522745163302</v>
+        <v>294.5856996654202</v>
       </c>
       <c r="W25">
-        <v>237.7536154795647</v>
+        <v>280.5774176468284</v>
       </c>
       <c r="Z25">
-        <v>2.907475570103267E-14</v>
+        <v>3.07282262834242E-14</v>
       </c>
       <c r="AA25">
-        <v>38.43538269739987</v>
+        <v>43.70482324975359</v>
       </c>
       <c r="AB25">
-        <v>62.46113373003445</v>
+        <v>73.2819932829555</v>
       </c>
       <c r="AC25">
-        <v>-6.834131042298808E-16</v>
+        <v>-3.031606512162975E-15</v>
       </c>
       <c r="AD25">
-        <v>1.465529619026646</v>
+        <v>1.406095956798671</v>
       </c>
       <c r="AE25">
-        <v>0.2035245335176227</v>
+        <v>11.73928277873525</v>
       </c>
       <c r="AF25">
-        <v>41.78808300395256</v>
+        <v>6.752811276429131</v>
       </c>
       <c r="AG25">
-        <v>0.4955297139477186</v>
+        <v>0.5513173933427098</v>
       </c>
       <c r="AH25">
-        <v>1886.928228833051</v>
+        <v>2074.150530314952</v>
       </c>
       <c r="AJ25">
-        <v>52.98510492994831</v>
+        <v>58.68854039693701</v>
       </c>
       <c r="AK25">
-        <v>388.3526037588097</v>
+        <v>439.837430523918</v>
       </c>
       <c r="AL25">
-        <v>103.5689471589262</v>
+        <v>98.23410853569644</v>
       </c>
       <c r="AM25">
-        <v>22.54667800327309</v>
+        <v>30.78268005879471</v>
       </c>
       <c r="AN25">
-        <v>17.57267767809051</v>
+        <v>18.77454162679426</v>
       </c>
       <c r="AO25">
-        <v>45.12898075030895</v>
+        <v>52.22162600539401</v>
       </c>
       <c r="AP25">
-        <v>2047.056157131697</v>
+        <v>2190.893646774453</v>
       </c>
       <c r="AQ25">
-        <v>220.7844359390267</v>
+        <v>240.3662410218267</v>
       </c>
       <c r="AR25">
-        <v>40.04323263320326</v>
+        <v>43.51724447513812</v>
       </c>
       <c r="AS25">
-        <v>13.99594655344655</v>
+        <v>15.14837801096192</v>
       </c>
       <c r="AT25">
-        <v>11.5149063071298</v>
+        <v>7.199172993492407</v>
       </c>
       <c r="AU25">
-        <v>172.578868312833</v>
+        <v>154.1675230044175</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3759,109 +3756,112 @@
         </is>
       </c>
       <c r="B26">
-        <v>412.3028757150286</v>
+        <v>463.2903564044502</v>
       </c>
       <c r="C26">
-        <v>68.1553571236342</v>
+        <v>80.57402293807972</v>
       </c>
       <c r="D26">
-        <v>5506.149992919936</v>
+        <v>6274.455596175976</v>
       </c>
       <c r="E26">
-        <v>591.1397280751723</v>
+        <v>310.432168250616</v>
       </c>
       <c r="F26">
-        <v>392.6142546254788</v>
+        <v>447.7377485709142</v>
       </c>
       <c r="G26">
-        <v>9.771001906742937</v>
+        <v>10.40423226372524</v>
       </c>
       <c r="I26">
-        <v>84.71993559662177</v>
+        <v>140.8477205942078</v>
       </c>
       <c r="J26">
-        <v>68.1553571236342</v>
+        <v>79.81991229169277</v>
+      </c>
+      <c r="K26">
+        <v>2.332340582741219E-14</v>
       </c>
       <c r="L26">
-        <v>3320.272240608769</v>
+        <v>3914.306004637754</v>
       </c>
       <c r="M26">
-        <v>793.0929940119761</v>
+        <v>859.4712572828766</v>
       </c>
       <c r="N26">
-        <v>1341.221655636919</v>
+        <v>1507.602756738879</v>
       </c>
       <c r="O26">
-        <v>500.7364721656119</v>
+        <v>250.0844375450463</v>
       </c>
       <c r="P26">
-        <v>17.6758475280248</v>
+        <v>10.37889148345158</v>
       </c>
       <c r="S26">
-        <v>17.28291297989017</v>
+        <v>23.37027093650077</v>
       </c>
       <c r="T26">
-        <v>5.599246240116626</v>
+        <v>6.410308417397057</v>
       </c>
       <c r="U26">
-        <v>7.101506412445067</v>
+        <v>10.32462992827074</v>
       </c>
       <c r="V26">
-        <v>92.88071731536925</v>
+        <v>98.16061836140993</v>
       </c>
       <c r="W26">
-        <v>259.2659101496013</v>
+        <v>300.3821506053923</v>
       </c>
       <c r="Z26">
-        <v>-2.790249363489688E-14</v>
+        <v>2.442108702054433E-14</v>
       </c>
       <c r="AA26">
-        <v>9.771001906742937</v>
+        <v>10.40423226372524</v>
       </c>
       <c r="AB26">
-        <v>2.384312818784458</v>
+        <v>0.02399476088160152</v>
       </c>
       <c r="AC26">
-        <v>-2.912333721256385E-16</v>
+        <v>-1.102746173377148E-15</v>
       </c>
       <c r="AH26">
-        <v>2088.409155974103</v>
+        <v>2321.047286890325</v>
       </c>
       <c r="AJ26">
-        <v>53.58810336176619</v>
+        <v>53.20409090909091</v>
       </c>
       <c r="AK26">
-        <v>642.6914030326272</v>
+        <v>792.1135683343243</v>
       </c>
       <c r="AL26">
-        <v>133.5460608036515</v>
+        <v>137.0174092720789</v>
       </c>
       <c r="AM26">
-        <v>91.01045691759418</v>
+        <v>135.8952846700602</v>
       </c>
       <c r="AN26">
-        <v>33.83623510054845</v>
+        <v>31.60479756660374</v>
       </c>
       <c r="AO26">
-        <v>70.03902342940042</v>
+        <v>69.06606770708282</v>
       </c>
       <c r="AP26">
-        <v>577.3191074318436</v>
+        <v>612.4700066144857</v>
       </c>
       <c r="AQ26">
-        <v>48.54583413693346</v>
+        <v>55.54182168056446</v>
       </c>
       <c r="AR26">
-        <v>8.161557141882202</v>
+        <v>2.888850558151738</v>
       </c>
       <c r="AS26">
-        <v>22.73843956260868</v>
+        <v>33.65693319313888</v>
       </c>
       <c r="AT26">
-        <v>5.140076548889752</v>
+        <v>6.420248954686492</v>
       </c>
       <c r="AU26">
-        <v>73.24246023148409</v>
+        <v>68.11602023417078</v>
       </c>
       <c r="AV26">
         <v>1</v>
@@ -3874,133 +3874,133 @@
         </is>
       </c>
       <c r="B27">
-        <v>894.6319683257918</v>
+        <v>984.6613464315574</v>
       </c>
       <c r="C27">
-        <v>94.70454481574328</v>
+        <v>96.85011402468436</v>
       </c>
       <c r="D27">
-        <v>5673.291404046161</v>
+        <v>6233.972346447952</v>
       </c>
       <c r="E27">
-        <v>275.2056963788302</v>
+        <v>336.657452133273</v>
       </c>
       <c r="F27">
-        <v>823.497388440289</v>
+        <v>903.521941924335</v>
       </c>
       <c r="G27">
-        <v>60.67483887213567</v>
+        <v>66.40553221288515</v>
       </c>
       <c r="H27">
-        <v>0.4721534516703475</v>
+        <v>0.7272419832720681</v>
       </c>
       <c r="I27">
-        <v>203.8051070011992</v>
+        <v>225.471025688377</v>
       </c>
       <c r="J27">
-        <v>59.37208112874779</v>
+        <v>61.91741285670048</v>
       </c>
       <c r="K27">
-        <v>8.590595903400602E-15</v>
+        <v>7.644815836747533E-15</v>
       </c>
       <c r="L27">
-        <v>2668.550733314768</v>
+        <v>2939.211647692496</v>
       </c>
       <c r="M27">
-        <v>2040.589618187293</v>
+        <v>2277.992139861865</v>
       </c>
       <c r="N27">
-        <v>830.3611933300012</v>
+        <v>881.0105422357938</v>
       </c>
       <c r="O27">
-        <v>107.6528922789539</v>
+        <v>141.8129115341545</v>
       </c>
       <c r="P27">
-        <v>53.8736686358754</v>
+        <v>53.5448124139083</v>
       </c>
       <c r="Q27">
-        <v>1.78953097169998</v>
+        <v>1.303768557289684</v>
       </c>
       <c r="R27">
-        <v>0.792845111020109</v>
+        <v>0.391877288361256</v>
       </c>
       <c r="S27">
-        <v>54.70714791328712</v>
+        <v>61.34563792507818</v>
       </c>
       <c r="T27">
-        <v>206.8325617432783</v>
+        <v>226.837930250117</v>
       </c>
       <c r="U27">
-        <v>85.96973507315144</v>
+        <v>90.90912729221913</v>
       </c>
       <c r="V27">
-        <v>308.0616352875268</v>
+        <v>311.6924208862998</v>
       </c>
       <c r="W27">
-        <v>184.3541421861846</v>
+        <v>216.9638113400127</v>
       </c>
       <c r="Z27">
-        <v>2.716171238659398E-14</v>
+        <v>3.985674411610244E-14</v>
       </c>
       <c r="AA27">
-        <v>22.03988213233325</v>
+        <v>24.57464470602892</v>
       </c>
       <c r="AB27">
-        <v>37.75504952234517</v>
+        <v>42.94120987706486</v>
       </c>
       <c r="AC27">
-        <v>5.538164765369648E-16</v>
+        <v>7.962875028518581E-16</v>
       </c>
       <c r="AD27">
-        <v>0.307617497435468</v>
+        <v>0.3071763771121409</v>
       </c>
       <c r="AE27">
-        <v>3.002366314441242</v>
+        <v>2.216957599118943</v>
       </c>
       <c r="AF27">
-        <v>39.87569167593464</v>
+        <v>36.47156060606061</v>
       </c>
       <c r="AG27">
-        <v>0.1307880490922552</v>
+        <v>0.1324166073286958</v>
       </c>
       <c r="AH27">
-        <v>2000.784968251244</v>
+        <v>2220.187604789995</v>
       </c>
       <c r="AJ27">
-        <v>52.48765572003988</v>
+        <v>54.12977607318107</v>
       </c>
       <c r="AK27">
-        <v>383.6692944920594</v>
+        <v>420.9186779911374</v>
       </c>
       <c r="AL27">
-        <v>102.5205061954837</v>
+        <v>94.53250177955429</v>
       </c>
       <c r="AM27">
-        <v>11.87765109301329</v>
+        <v>13.85927303244079</v>
       </c>
       <c r="AN27">
-        <v>17.78045817150088</v>
+        <v>18.28115856201518</v>
       </c>
       <c r="AO27">
-        <v>55.07179036719013</v>
+        <v>54.13188763275099</v>
       </c>
       <c r="AP27">
-        <v>1467.133999055319</v>
+        <v>1632.630091790289</v>
       </c>
       <c r="AQ27">
-        <v>245.4223091275468</v>
+        <v>266.8468977311195</v>
       </c>
       <c r="AR27">
-        <v>95.79249966978031</v>
+        <v>132.4788648821375</v>
       </c>
       <c r="AS27">
-        <v>8.681848832901075</v>
+        <v>16.1118327588759</v>
       </c>
       <c r="AT27">
-        <v>3.495540562606495</v>
+        <v>3.049027973493434</v>
       </c>
       <c r="AU27">
-        <v>161.15832593532</v>
+        <v>161.6110102802398</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,124 +4013,127 @@
         </is>
       </c>
       <c r="B28">
-        <v>321.9315</v>
+        <v>501.3242046659597</v>
       </c>
       <c r="C28">
-        <v>44.70067903729222</v>
+        <v>46.31299189401768</v>
       </c>
       <c r="D28">
-        <v>7807.271022463207</v>
+        <v>8260.657360562143</v>
       </c>
       <c r="E28">
-        <v>141.55996664443</v>
+        <v>159.4887790697674</v>
       </c>
       <c r="F28">
-        <v>308.7471887201735</v>
+        <v>466.1273370754448</v>
       </c>
       <c r="G28">
-        <v>7.282690746753246</v>
+        <v>10.71684719963952</v>
       </c>
       <c r="H28">
-        <v>13.61874682096545</v>
+        <v>10.99809000707175</v>
       </c>
       <c r="I28">
-        <v>246.6593167892157</v>
+        <v>157.9050703971119</v>
       </c>
       <c r="J28">
-        <v>25.12364093337563</v>
+        <v>29.30850253023861</v>
       </c>
       <c r="K28">
-        <v>5.258936387303184E-15</v>
+        <v>-2.516802959798617E-15</v>
       </c>
       <c r="L28">
-        <v>4771.457411019015</v>
+        <v>5015.987195200342</v>
       </c>
       <c r="M28">
-        <v>1449.732113275706</v>
+        <v>1732.004210836278</v>
       </c>
       <c r="N28">
-        <v>1513.924335894623</v>
+        <v>1431.829684960481</v>
       </c>
       <c r="O28">
-        <v>107.5393355173105</v>
+        <v>119.246338028169</v>
       </c>
       <c r="P28">
-        <v>47.36740755317493</v>
+        <v>25.56626248708233</v>
       </c>
       <c r="Q28">
-        <v>2.053648068669528</v>
+        <v>0.9081785102739727</v>
       </c>
       <c r="S28">
-        <v>1.529955183268587</v>
+        <v>1.056811757628068</v>
       </c>
       <c r="T28">
-        <v>5.096193228736581</v>
+        <v>13.60980841330315</v>
       </c>
       <c r="U28">
-        <v>101.86106607536</v>
+        <v>99.55552768684092</v>
       </c>
       <c r="V28">
-        <v>178.6345279912184</v>
+        <v>182.2088268389248</v>
       </c>
       <c r="W28">
-        <v>94.3693944967407</v>
+        <v>130.0576689189189</v>
       </c>
       <c r="Z28">
-        <v>8.351769985431868E-15</v>
+        <v>1.271603733773182E-14</v>
       </c>
       <c r="AA28">
-        <v>2.679369936742547</v>
+        <v>4.316036513545347</v>
       </c>
       <c r="AB28">
-        <v>4.599404729546072</v>
+        <v>4.647012211668929</v>
       </c>
       <c r="AC28">
-        <v>-9.286243636644151E-17</v>
+        <v>7.707582218414647E-17</v>
+      </c>
+      <c r="AD28">
+        <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>17.10480134295967</v>
+        <v>17.3006440061268</v>
       </c>
       <c r="AG28">
-        <v>1.497372081470442</v>
+        <v>1.699354707792208</v>
       </c>
       <c r="AH28">
-        <v>3070.198420599009</v>
+        <v>3243.038623721881</v>
       </c>
       <c r="AJ28">
-        <v>88.00306716929404</v>
+        <v>74.95777747625507</v>
       </c>
       <c r="AK28">
-        <v>843.5377586206897</v>
+        <v>1025.54998268262</v>
       </c>
       <c r="AL28">
-        <v>138.97204902577</v>
+        <v>118.6586219031531</v>
       </c>
       <c r="AM28">
-        <v>29.79354953408534</v>
+        <v>60.42723063954682</v>
       </c>
       <c r="AN28">
-        <v>68.8615669633231</v>
+        <v>48.12835278154682</v>
       </c>
       <c r="AO28">
-        <v>185.3645135433943</v>
+        <v>138.5282464581668</v>
       </c>
       <c r="AP28">
-        <v>1024.463842028279</v>
+        <v>1179.840509013786</v>
       </c>
       <c r="AQ28">
-        <v>76.98881046054154</v>
+        <v>80.44934871794872</v>
       </c>
       <c r="AR28">
-        <v>7.611479273622844</v>
+        <v>15.52628247834777</v>
       </c>
       <c r="AS28">
-        <v>7.678266095832633</v>
+        <v>6.807825722664433</v>
       </c>
       <c r="AT28">
-        <v>1.678903495979287</v>
+        <v>3.031521572910978</v>
       </c>
       <c r="AU28">
-        <v>266.7611472972982</v>
+        <v>350.8799200685126</v>
       </c>
       <c r="AV28">
         <v>1</v>
